--- a/幽灵歌单整理.xlsx
+++ b/幽灵歌单整理.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Ksoftware\v-song-list-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03FC5D37-6670-4EFF-B3B1-113436F99EFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CCA1236-875D-4540-9A64-4C85DFB4C772}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1786,9 +1786,6 @@
     <t>杨丞琳</t>
   </si>
   <si>
-    <t>雨爱</t>
-  </si>
-  <si>
     <t>左边</t>
   </si>
   <si>
@@ -3001,6 +2998,10 @@
   </si>
   <si>
     <t>绿光(绿光在哪里）</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>雨爱(remix)</t>
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
 </sst>
@@ -3135,45 +3136,45 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -3521,7 +3522,7 @@
         <v>7</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>8</v>
@@ -3620,7 +3621,7 @@
         <v>20</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>8</v>
@@ -3774,7 +3775,7 @@
         <v>22</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>12</v>
@@ -3890,7 +3891,7 @@
         <v>39</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>8</v>
@@ -4008,7 +4009,7 @@
         <v>56</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="E28" s="4" t="s">
         <v>57</v>
@@ -4067,7 +4068,7 @@
         <v>64</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="E31" s="6" t="s">
         <v>8</v>
@@ -4090,7 +4091,7 @@
         <v>67</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="E32" s="4" t="s">
         <v>8</v>
@@ -4111,7 +4112,7 @@
         <v>69</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="E33" s="6" t="s">
         <v>60</v>
@@ -4286,7 +4287,7 @@
         <v>87</v>
       </c>
       <c r="D42" s="8" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>12</v>
@@ -4442,7 +4443,7 @@
         <v>102</v>
       </c>
       <c r="D50" s="8" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>8</v>
@@ -4465,7 +4466,7 @@
         <v>105</v>
       </c>
       <c r="D51" s="8" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="E51" s="6" t="s">
         <v>8</v>
@@ -4505,7 +4506,7 @@
         <v>109</v>
       </c>
       <c r="D53" s="8" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="E53" s="4" t="s">
         <v>8</v>
@@ -4568,7 +4569,7 @@
         <v>116</v>
       </c>
       <c r="D56" s="8" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>8</v>
@@ -4665,7 +4666,7 @@
         <v>126</v>
       </c>
       <c r="D61" s="8" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="E61" s="6" t="s">
         <v>127</v>
@@ -4819,7 +4820,7 @@
         <v>140</v>
       </c>
       <c r="D69" s="8" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="E69" s="6" t="s">
         <v>12</v>
@@ -4859,7 +4860,7 @@
         <v>144</v>
       </c>
       <c r="D71" s="8" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="E71" s="6" t="s">
         <v>60</v>
@@ -5129,7 +5130,7 @@
         <v>165</v>
       </c>
       <c r="D85" s="8" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="E85" s="6" t="s">
         <v>18</v>
@@ -5150,7 +5151,7 @@
         <v>168</v>
       </c>
       <c r="D86" s="8" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>54</v>
@@ -5190,7 +5191,7 @@
         <v>170</v>
       </c>
       <c r="D88" s="8" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>8</v>
@@ -5211,7 +5212,7 @@
         <v>170</v>
       </c>
       <c r="D89" s="8" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E89" s="6" t="s">
         <v>48</v>
@@ -5270,7 +5271,7 @@
         <v>177</v>
       </c>
       <c r="D92" s="8" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>8</v>
@@ -5312,7 +5313,7 @@
         <v>182</v>
       </c>
       <c r="D94" s="8" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>12</v>
@@ -5485,7 +5486,7 @@
         <v>197</v>
       </c>
       <c r="D103" s="8" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="E103" s="6" t="s">
         <v>12</v>
@@ -5506,7 +5507,7 @@
         <v>199</v>
       </c>
       <c r="D104" s="8" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>12</v>
@@ -5643,7 +5644,7 @@
         <v>209</v>
       </c>
       <c r="D111" s="8" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="E111" s="6" t="s">
         <v>12</v>
@@ -5856,7 +5857,7 @@
         <v>234</v>
       </c>
       <c r="D122" s="8" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>8</v>
@@ -6086,7 +6087,7 @@
         <v>257</v>
       </c>
       <c r="D134" s="8" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="E134" s="6" t="s">
         <v>258</v>
@@ -6202,7 +6203,7 @@
         <v>271</v>
       </c>
       <c r="D140" s="8" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="E140" s="6" t="s">
         <v>12</v>
@@ -6223,7 +6224,7 @@
         <v>273</v>
       </c>
       <c r="D141" s="8" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="E141" s="6" t="s">
         <v>12</v>
@@ -6244,7 +6245,7 @@
         <v>275</v>
       </c>
       <c r="D142" s="8" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="E142" s="6" t="s">
         <v>48</v>
@@ -6957,7 +6958,7 @@
         <v>338</v>
       </c>
       <c r="D179" s="8" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="E179" s="6" t="s">
         <v>8</v>
@@ -7001,7 +7002,7 @@
         <v>341</v>
       </c>
       <c r="D181" s="8" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E181" s="6" t="s">
         <v>54</v>
@@ -7022,7 +7023,7 @@
         <v>341</v>
       </c>
       <c r="D182" s="8" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="E182" s="6" t="s">
         <v>12</v>
@@ -7081,7 +7082,7 @@
         <v>341</v>
       </c>
       <c r="D185" s="8" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="E185" s="6" t="s">
         <v>12</v>
@@ -7163,7 +7164,7 @@
         <v>354</v>
       </c>
       <c r="D189" s="8" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="E189" s="6" t="s">
         <v>12</v>
@@ -7184,7 +7185,7 @@
         <v>356</v>
       </c>
       <c r="D190" s="8" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E190" s="6" t="s">
         <v>12</v>
@@ -7205,7 +7206,7 @@
         <v>358</v>
       </c>
       <c r="D191" s="8" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="E191" s="6" t="s">
         <v>48</v>
@@ -7401,7 +7402,7 @@
         <v>380</v>
       </c>
       <c r="D201" s="8" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="E201" s="6" t="s">
         <v>54</v>
@@ -7479,7 +7480,7 @@
         <v>380</v>
       </c>
       <c r="D205" s="8" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="E205" s="6" t="s">
         <v>12</v>
@@ -7519,7 +7520,7 @@
         <v>380</v>
       </c>
       <c r="D207" s="8" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="E207" s="6" t="s">
         <v>12</v>
@@ -7597,7 +7598,7 @@
         <v>380</v>
       </c>
       <c r="D211" s="8" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="E211" s="6" t="s">
         <v>12</v>
@@ -7620,7 +7621,7 @@
         <v>380</v>
       </c>
       <c r="D212" s="8" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="E212" s="3" t="s">
         <v>48</v>
@@ -7679,7 +7680,7 @@
         <v>380</v>
       </c>
       <c r="D215" s="8" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="E215" s="6" t="s">
         <v>12</v>
@@ -7740,7 +7741,7 @@
         <v>380</v>
       </c>
       <c r="D218" s="8" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="E218" s="6" t="s">
         <v>34</v>
@@ -7761,7 +7762,7 @@
         <v>400</v>
       </c>
       <c r="D219" s="8" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="E219" s="6" t="s">
         <v>12</v>
@@ -7801,7 +7802,7 @@
         <v>403</v>
       </c>
       <c r="D221" s="8" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="E221" s="6" t="s">
         <v>12</v>
@@ -7879,7 +7880,7 @@
         <v>409</v>
       </c>
       <c r="D225" s="8" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="E225" s="6" t="s">
         <v>12</v>
@@ -7957,7 +7958,7 @@
         <v>415</v>
       </c>
       <c r="D229" s="8" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="E229" s="6" t="s">
         <v>12</v>
@@ -7997,7 +7998,7 @@
         <v>420</v>
       </c>
       <c r="D231" s="8" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="E231" s="6" t="s">
         <v>12</v>
@@ -8018,7 +8019,7 @@
         <v>422</v>
       </c>
       <c r="D232" s="8" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="E232" s="6" t="s">
         <v>12</v>
@@ -8098,7 +8099,7 @@
         <v>431</v>
       </c>
       <c r="D236" s="8" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="E236" s="6" t="s">
         <v>8</v>
@@ -8178,7 +8179,7 @@
         <v>438</v>
       </c>
       <c r="D240" s="8" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="E240" s="6" t="s">
         <v>54</v>
@@ -8351,7 +8352,7 @@
         <v>320</v>
       </c>
       <c r="D249" s="8" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="E249" s="6" t="s">
         <v>452</v>
@@ -8395,7 +8396,7 @@
         <v>457</v>
       </c>
       <c r="D251" s="8" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="E251" s="3" t="s">
         <v>48</v>
@@ -8456,7 +8457,7 @@
         <v>464</v>
       </c>
       <c r="D254" s="8" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="E254" s="6" t="s">
         <v>8</v>
@@ -8557,7 +8558,7 @@
         <v>475</v>
       </c>
       <c r="D259" s="8" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="E259" s="6" t="s">
         <v>8</v>
@@ -8639,7 +8640,7 @@
         <v>485</v>
       </c>
       <c r="D263" s="8" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="E263" s="6" t="s">
         <v>54</v>
@@ -8812,7 +8813,7 @@
         <v>496</v>
       </c>
       <c r="D272" s="8" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="E272" s="6" t="s">
         <v>12</v>
@@ -8827,7 +8828,7 @@
     <row r="273" spans="1:11" ht="16.5">
       <c r="A273" s="4"/>
       <c r="B273" s="5" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="C273" s="6" t="s">
         <v>496</v>
@@ -8928,7 +8929,7 @@
         <v>506</v>
       </c>
       <c r="D278" s="8" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="E278" s="4" t="s">
         <v>57</v>
@@ -9354,7 +9355,7 @@
         <v>544</v>
       </c>
       <c r="D300" s="8" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="E300" s="6" t="s">
         <v>12</v>
@@ -9643,7 +9644,7 @@
         <v>567</v>
       </c>
       <c r="D315" s="8" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="E315" s="6" t="s">
         <v>12</v>
@@ -9829,7 +9830,7 @@
     <row r="325" spans="1:11" ht="16.5">
       <c r="A325" s="4"/>
       <c r="B325" s="5" t="s">
-        <v>588</v>
+        <v>758</v>
       </c>
       <c r="C325" s="6" t="s">
         <v>587</v>
@@ -9848,7 +9849,7 @@
     <row r="326" spans="1:11" ht="16.5">
       <c r="A326" s="4"/>
       <c r="B326" s="5" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="C326" s="6" t="s">
         <v>587</v>
@@ -9867,10 +9868,10 @@
     <row r="327" spans="1:11" ht="16.5">
       <c r="A327" s="4"/>
       <c r="B327" s="5" t="s">
+        <v>589</v>
+      </c>
+      <c r="C327" s="6" t="s">
         <v>590</v>
-      </c>
-      <c r="C327" s="6" t="s">
-        <v>591</v>
       </c>
       <c r="D327" s="4"/>
       <c r="E327" s="6" t="s">
@@ -9886,10 +9887,10 @@
     <row r="328" spans="1:11" ht="16.5">
       <c r="A328" s="4"/>
       <c r="B328" s="5" t="s">
+        <v>591</v>
+      </c>
+      <c r="C328" s="6" t="s">
         <v>592</v>
-      </c>
-      <c r="C328" s="6" t="s">
-        <v>593</v>
       </c>
       <c r="D328" s="4"/>
       <c r="E328" s="6" t="s">
@@ -9905,10 +9906,10 @@
     <row r="329" spans="1:11" ht="16.5">
       <c r="A329" s="4"/>
       <c r="B329" s="5" t="s">
+        <v>593</v>
+      </c>
+      <c r="C329" s="6" t="s">
         <v>594</v>
-      </c>
-      <c r="C329" s="6" t="s">
-        <v>595</v>
       </c>
       <c r="D329" s="4"/>
       <c r="E329" s="6" t="s">
@@ -9924,14 +9925,14 @@
     <row r="330" spans="1:11" ht="16.5">
       <c r="A330" s="4"/>
       <c r="B330" s="5" t="s">
+        <v>595</v>
+      </c>
+      <c r="C330" s="6" t="s">
         <v>596</v>
-      </c>
-      <c r="C330" s="6" t="s">
-        <v>597</v>
       </c>
       <c r="D330" s="4"/>
       <c r="E330" s="6" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="F330" s="4"/>
       <c r="G330" s="4"/>
@@ -9943,10 +9944,10 @@
     <row r="331" spans="1:11" ht="16.5">
       <c r="A331" s="4"/>
       <c r="B331" s="5" t="s">
+        <v>598</v>
+      </c>
+      <c r="C331" s="6" t="s">
         <v>599</v>
-      </c>
-      <c r="C331" s="6" t="s">
-        <v>600</v>
       </c>
       <c r="D331" s="4"/>
       <c r="E331" s="6" t="s">
@@ -9962,10 +9963,10 @@
     <row r="332" spans="1:11" ht="16.5">
       <c r="A332" s="4"/>
       <c r="B332" s="5" t="s">
+        <v>600</v>
+      </c>
+      <c r="C332" s="6" t="s">
         <v>601</v>
-      </c>
-      <c r="C332" s="6" t="s">
-        <v>602</v>
       </c>
       <c r="D332" s="4"/>
       <c r="E332" s="6" t="s">
@@ -9981,10 +9982,10 @@
     <row r="333" spans="1:11" ht="16.5">
       <c r="A333" s="4"/>
       <c r="B333" s="5" t="s">
+        <v>602</v>
+      </c>
+      <c r="C333" s="6" t="s">
         <v>603</v>
-      </c>
-      <c r="C333" s="6" t="s">
-        <v>604</v>
       </c>
       <c r="D333" s="4"/>
       <c r="E333" s="6" t="s">
@@ -10000,10 +10001,10 @@
     <row r="334" spans="1:11" ht="16.5">
       <c r="A334" s="4"/>
       <c r="B334" s="5" t="s">
+        <v>604</v>
+      </c>
+      <c r="C334" s="6" t="s">
         <v>605</v>
-      </c>
-      <c r="C334" s="6" t="s">
-        <v>606</v>
       </c>
       <c r="D334" s="4"/>
       <c r="E334" s="6" t="s">
@@ -10019,10 +10020,10 @@
     <row r="335" spans="1:11" ht="16.5">
       <c r="A335" s="4"/>
       <c r="B335" s="5" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="C335" s="6" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="D335" s="4"/>
       <c r="E335" s="6" t="s">
@@ -10038,10 +10039,10 @@
     <row r="336" spans="1:11" ht="16.5">
       <c r="A336" s="4"/>
       <c r="B336" s="5" t="s">
+        <v>607</v>
+      </c>
+      <c r="C336" s="6" t="s">
         <v>608</v>
-      </c>
-      <c r="C336" s="6" t="s">
-        <v>609</v>
       </c>
       <c r="D336" s="4"/>
       <c r="E336" s="6" t="s">
@@ -10057,17 +10058,17 @@
     <row r="337" spans="1:11" ht="16.5">
       <c r="A337" s="4"/>
       <c r="B337" s="5" t="s">
+        <v>609</v>
+      </c>
+      <c r="C337" s="6" t="s">
         <v>610</v>
-      </c>
-      <c r="C337" s="6" t="s">
-        <v>611</v>
       </c>
       <c r="D337" s="4"/>
       <c r="E337" s="6" t="s">
         <v>54</v>
       </c>
       <c r="F337" s="6" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="G337" s="4"/>
       <c r="H337" s="4"/>
@@ -10078,19 +10079,19 @@
     <row r="338" spans="1:11" ht="16.5">
       <c r="A338" s="4"/>
       <c r="B338" s="9" t="s">
+        <v>612</v>
+      </c>
+      <c r="C338" s="6" t="s">
         <v>613</v>
       </c>
-      <c r="C338" s="6" t="s">
-        <v>614</v>
-      </c>
       <c r="D338" s="8" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="E338" s="6" t="s">
         <v>8</v>
       </c>
       <c r="F338" s="6" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="G338" s="4"/>
       <c r="H338" s="4"/>
@@ -10101,10 +10102,10 @@
     <row r="339" spans="1:11" ht="16.5">
       <c r="A339" s="4"/>
       <c r="B339" s="5" t="s">
+        <v>615</v>
+      </c>
+      <c r="C339" s="6" t="s">
         <v>616</v>
-      </c>
-      <c r="C339" s="6" t="s">
-        <v>617</v>
       </c>
       <c r="D339" s="4"/>
       <c r="E339" s="6" t="s">
@@ -10120,10 +10121,10 @@
     <row r="340" spans="1:11" ht="16.5">
       <c r="A340" s="4"/>
       <c r="B340" s="9" t="s">
+        <v>617</v>
+      </c>
+      <c r="C340" s="6" t="s">
         <v>618</v>
-      </c>
-      <c r="C340" s="6" t="s">
-        <v>619</v>
       </c>
       <c r="D340" s="4"/>
       <c r="E340" s="6" t="s">
@@ -10139,13 +10140,13 @@
     <row r="341" spans="1:11" ht="16.5">
       <c r="A341" s="4"/>
       <c r="B341" s="9" t="s">
+        <v>619</v>
+      </c>
+      <c r="C341" s="15" t="s">
         <v>620</v>
       </c>
-      <c r="C341" s="15" t="s">
-        <v>621</v>
-      </c>
       <c r="D341" s="8" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="E341" s="6" t="s">
         <v>127</v>
@@ -10160,10 +10161,10 @@
     <row r="342" spans="1:11" ht="16.5">
       <c r="A342" s="4"/>
       <c r="B342" s="9" t="s">
+        <v>621</v>
+      </c>
+      <c r="C342" s="6" t="s">
         <v>622</v>
-      </c>
-      <c r="C342" s="6" t="s">
-        <v>623</v>
       </c>
       <c r="D342" s="4"/>
       <c r="E342" s="6" t="s">
@@ -10179,10 +10180,10 @@
     <row r="343" spans="1:11" ht="16.5">
       <c r="A343" s="4"/>
       <c r="B343" s="5" t="s">
+        <v>623</v>
+      </c>
+      <c r="C343" s="6" t="s">
         <v>624</v>
-      </c>
-      <c r="C343" s="6" t="s">
-        <v>625</v>
       </c>
       <c r="D343" s="4"/>
       <c r="E343" s="6" t="s">
@@ -10198,10 +10199,10 @@
     <row r="344" spans="1:11" ht="16.5">
       <c r="A344" s="4"/>
       <c r="B344" s="5" t="s">
+        <v>625</v>
+      </c>
+      <c r="C344" s="6" t="s">
         <v>626</v>
-      </c>
-      <c r="C344" s="6" t="s">
-        <v>627</v>
       </c>
       <c r="D344" s="4"/>
       <c r="E344" s="6" t="s">
@@ -10217,10 +10218,10 @@
     <row r="345" spans="1:11" ht="16.5">
       <c r="A345" s="4"/>
       <c r="B345" s="5" t="s">
+        <v>627</v>
+      </c>
+      <c r="C345" s="6" t="s">
         <v>628</v>
-      </c>
-      <c r="C345" s="6" t="s">
-        <v>629</v>
       </c>
       <c r="D345" s="4"/>
       <c r="E345" s="6" t="s">
@@ -10236,10 +10237,10 @@
     <row r="346" spans="1:11" ht="16.5">
       <c r="A346" s="4"/>
       <c r="B346" s="5" t="s">
+        <v>629</v>
+      </c>
+      <c r="C346" s="6" t="s">
         <v>630</v>
-      </c>
-      <c r="C346" s="6" t="s">
-        <v>631</v>
       </c>
       <c r="D346" s="4"/>
       <c r="E346" s="6" t="s">
@@ -10255,10 +10256,10 @@
     <row r="347" spans="1:11" ht="16.5">
       <c r="A347" s="4"/>
       <c r="B347" s="5" t="s">
+        <v>631</v>
+      </c>
+      <c r="C347" s="6" t="s">
         <v>632</v>
-      </c>
-      <c r="C347" s="6" t="s">
-        <v>633</v>
       </c>
       <c r="D347" s="4"/>
       <c r="E347" s="6" t="s">
@@ -10274,14 +10275,14 @@
     <row r="348" spans="1:11" ht="16.5">
       <c r="A348" s="4"/>
       <c r="B348" s="5" t="s">
+        <v>633</v>
+      </c>
+      <c r="C348" s="6" t="s">
         <v>634</v>
-      </c>
-      <c r="C348" s="6" t="s">
-        <v>635</v>
       </c>
       <c r="D348" s="4"/>
       <c r="E348" s="6" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="F348" s="4"/>
       <c r="G348" s="4"/>
@@ -10293,14 +10294,14 @@
     <row r="349" spans="1:11" ht="16.5">
       <c r="A349" s="4"/>
       <c r="B349" s="9" t="s">
+        <v>636</v>
+      </c>
+      <c r="C349" s="10" t="s">
         <v>637</v>
-      </c>
-      <c r="C349" s="10" t="s">
-        <v>638</v>
       </c>
       <c r="D349" s="11"/>
       <c r="E349" s="6" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="F349" s="4"/>
       <c r="G349" s="4"/>
@@ -10312,10 +10313,10 @@
     <row r="350" spans="1:11" ht="16.5">
       <c r="A350" s="4"/>
       <c r="B350" s="5" t="s">
+        <v>639</v>
+      </c>
+      <c r="C350" s="6" t="s">
         <v>640</v>
-      </c>
-      <c r="C350" s="6" t="s">
-        <v>641</v>
       </c>
       <c r="D350" s="4"/>
       <c r="E350" s="6" t="s">
@@ -10331,10 +10332,10 @@
     <row r="351" spans="1:11" ht="16.5">
       <c r="A351" s="4"/>
       <c r="B351" s="5" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C351" s="6" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D351" s="4"/>
       <c r="E351" s="6" t="s">
@@ -10350,10 +10351,10 @@
     <row r="352" spans="1:11" ht="16.5">
       <c r="A352" s="4"/>
       <c r="B352" s="5" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="C352" s="6" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D352" s="4"/>
       <c r="E352" s="6" t="s">
@@ -10369,10 +10370,10 @@
     <row r="353" spans="1:11" ht="16.5">
       <c r="A353" s="4"/>
       <c r="B353" s="5" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="C353" s="6" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D353" s="4"/>
       <c r="E353" s="6" t="s">
@@ -10388,10 +10389,10 @@
     <row r="354" spans="1:11" ht="16.5">
       <c r="A354" s="4"/>
       <c r="B354" s="5" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="C354" s="6" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D354" s="4"/>
       <c r="E354" s="6" t="s">
@@ -10407,10 +10408,10 @@
     <row r="355" spans="1:11" ht="16.5">
       <c r="A355" s="4"/>
       <c r="B355" s="5" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="C355" s="6" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D355" s="4"/>
       <c r="E355" s="6" t="s">
@@ -10426,10 +10427,10 @@
     <row r="356" spans="1:11" ht="16.5">
       <c r="A356" s="4"/>
       <c r="B356" s="5" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="C356" s="6" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D356" s="4"/>
       <c r="E356" s="6" t="s">
@@ -10445,10 +10446,10 @@
     <row r="357" spans="1:11" ht="16.5">
       <c r="A357" s="4"/>
       <c r="B357" s="5" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="C357" s="6" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D357" s="4"/>
       <c r="E357" s="6" t="s">
@@ -10464,10 +10465,10 @@
     <row r="358" spans="1:11" ht="16.5">
       <c r="A358" s="4"/>
       <c r="B358" s="5" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="C358" s="6" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D358" s="4"/>
       <c r="E358" s="12" t="s">
@@ -10483,10 +10484,10 @@
     <row r="359" spans="1:11" ht="16.5">
       <c r="A359" s="4"/>
       <c r="B359" s="5" t="s">
+        <v>649</v>
+      </c>
+      <c r="C359" s="6" t="s">
         <v>650</v>
-      </c>
-      <c r="C359" s="6" t="s">
-        <v>651</v>
       </c>
       <c r="D359" s="4"/>
       <c r="E359" s="6" t="s">
@@ -10502,10 +10503,10 @@
     <row r="360" spans="1:11" ht="16.5">
       <c r="A360" s="4"/>
       <c r="B360" s="5" t="s">
+        <v>651</v>
+      </c>
+      <c r="C360" s="6" t="s">
         <v>652</v>
-      </c>
-      <c r="C360" s="6" t="s">
-        <v>653</v>
       </c>
       <c r="D360" s="4"/>
       <c r="E360" s="6" t="s">
@@ -10521,17 +10522,17 @@
     <row r="361" spans="1:11" ht="16.5">
       <c r="A361" s="4"/>
       <c r="B361" s="5" t="s">
+        <v>653</v>
+      </c>
+      <c r="C361" s="6" t="s">
         <v>654</v>
-      </c>
-      <c r="C361" s="6" t="s">
-        <v>655</v>
       </c>
       <c r="D361" s="4"/>
       <c r="E361" s="6" t="s">
         <v>34</v>
       </c>
       <c r="F361" s="6" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="G361" s="4"/>
       <c r="H361" s="4"/>
@@ -10542,10 +10543,10 @@
     <row r="362" spans="1:11" ht="16.5">
       <c r="A362" s="4"/>
       <c r="B362" s="5" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="C362" s="6" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="D362" s="4"/>
       <c r="E362" s="6" t="s">
@@ -10561,10 +10562,10 @@
     <row r="363" spans="1:11" ht="16.5">
       <c r="A363" s="4"/>
       <c r="B363" s="5" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="C363" s="6" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="D363" s="4"/>
       <c r="E363" s="6" t="s">
@@ -10580,10 +10581,10 @@
     <row r="364" spans="1:11" ht="16.5">
       <c r="A364" s="4"/>
       <c r="B364" s="5" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="C364" s="6" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="D364" s="4"/>
       <c r="E364" s="6" t="s">
@@ -10599,10 +10600,10 @@
     <row r="365" spans="1:11" ht="16.5">
       <c r="A365" s="4"/>
       <c r="B365" s="5" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="C365" s="6" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="D365" s="4"/>
       <c r="E365" s="6" t="s">
@@ -10618,10 +10619,10 @@
     <row r="366" spans="1:11" ht="16.5">
       <c r="A366" s="4"/>
       <c r="B366" s="5" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="C366" s="6" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="D366" s="4"/>
       <c r="E366" s="6" t="s">
@@ -10637,10 +10638,10 @@
     <row r="367" spans="1:11" ht="16.5">
       <c r="A367" s="4"/>
       <c r="B367" s="5" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="C367" s="6" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="D367" s="4"/>
       <c r="E367" s="6" t="s">
@@ -10656,10 +10657,10 @@
     <row r="368" spans="1:11" ht="16.5">
       <c r="A368" s="4"/>
       <c r="B368" s="5" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="C368" s="6" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="D368" s="4"/>
       <c r="E368" s="6" t="s">
@@ -10675,10 +10676,10 @@
     <row r="369" spans="1:11" ht="16.5">
       <c r="A369" s="4"/>
       <c r="B369" s="2" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="C369" s="6" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="D369" s="4"/>
       <c r="E369" s="6" t="s">
@@ -10694,10 +10695,10 @@
     <row r="370" spans="1:11" ht="16.5">
       <c r="A370" s="4"/>
       <c r="B370" s="5" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="C370" s="6" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="D370" s="4"/>
       <c r="E370" s="6" t="s">
@@ -10713,10 +10714,10 @@
     <row r="371" spans="1:11" ht="16.5">
       <c r="A371" s="4"/>
       <c r="B371" s="5" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="C371" s="6" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="D371" s="4"/>
       <c r="E371" s="6" t="s">
@@ -10732,10 +10733,10 @@
     <row r="372" spans="1:11" ht="16.5">
       <c r="A372" s="4"/>
       <c r="B372" s="5" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="C372" s="6" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="D372" s="4"/>
       <c r="E372" s="6" t="s">
@@ -10751,10 +10752,10 @@
     <row r="373" spans="1:11" ht="16.5">
       <c r="A373" s="4"/>
       <c r="B373" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="C373" s="6" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="D373" s="4"/>
       <c r="E373" s="6" t="s">
@@ -10770,10 +10771,10 @@
     <row r="374" spans="1:11" ht="16.5">
       <c r="A374" s="4"/>
       <c r="B374" s="5" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="C374" s="6" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="D374" s="4"/>
       <c r="E374" s="6" t="s">
@@ -10789,10 +10790,10 @@
     <row r="375" spans="1:11" ht="16.5">
       <c r="A375" s="4"/>
       <c r="B375" s="5" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="C375" s="6" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="D375" s="4"/>
       <c r="E375" s="6" t="s">
@@ -10808,10 +10809,10 @@
     <row r="376" spans="1:11" ht="16.5">
       <c r="A376" s="4"/>
       <c r="B376" s="5" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="C376" s="6" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="D376" s="4"/>
       <c r="E376" s="6" t="s">
@@ -10827,10 +10828,10 @@
     <row r="377" spans="1:11" ht="16.5">
       <c r="A377" s="4"/>
       <c r="B377" s="5" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="C377" s="6" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="D377" s="4"/>
       <c r="E377" s="6" t="s">
@@ -10846,10 +10847,10 @@
     <row r="378" spans="1:11" ht="16.5">
       <c r="A378" s="4"/>
       <c r="B378" s="5" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="C378" s="6" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="D378" s="4"/>
       <c r="E378" s="6" t="s">
@@ -10865,10 +10866,10 @@
     <row r="379" spans="1:11" ht="16.5">
       <c r="A379" s="4"/>
       <c r="B379" s="5" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="C379" s="6" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="D379" s="4"/>
       <c r="E379" s="6" t="s">
@@ -10884,10 +10885,10 @@
     <row r="380" spans="1:11" ht="16.5">
       <c r="A380" s="4"/>
       <c r="B380" s="5" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="C380" s="6" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="D380" s="4"/>
       <c r="E380" s="6" t="s">
@@ -10903,10 +10904,10 @@
     <row r="381" spans="1:11" ht="16.5">
       <c r="A381" s="4"/>
       <c r="B381" s="5" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="C381" s="6" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="D381" s="4"/>
       <c r="E381" s="6" t="s">
@@ -10922,10 +10923,10 @@
     <row r="382" spans="1:11" ht="16.5">
       <c r="A382" s="4"/>
       <c r="B382" s="5" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="C382" s="6" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="D382" s="4"/>
       <c r="E382" s="6" t="s">
@@ -10941,10 +10942,10 @@
     <row r="383" spans="1:11" ht="16.5">
       <c r="A383" s="4"/>
       <c r="B383" s="5" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="C383" s="6" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="D383" s="4"/>
       <c r="E383" s="6" t="s">
@@ -10960,10 +10961,10 @@
     <row r="384" spans="1:11" ht="16.5">
       <c r="A384" s="4"/>
       <c r="B384" s="5" t="s">
+        <v>678</v>
+      </c>
+      <c r="C384" s="6" t="s">
         <v>679</v>
-      </c>
-      <c r="C384" s="6" t="s">
-        <v>680</v>
       </c>
       <c r="D384" s="4"/>
       <c r="E384" s="6" t="s">
@@ -10979,13 +10980,13 @@
     <row r="385" spans="1:11" ht="16.5">
       <c r="A385" s="4"/>
       <c r="B385" s="5" t="s">
+        <v>680</v>
+      </c>
+      <c r="C385" s="6" t="s">
         <v>681</v>
       </c>
-      <c r="C385" s="6" t="s">
-        <v>682</v>
-      </c>
       <c r="D385" s="8" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="E385" s="6" t="s">
         <v>12</v>
@@ -11000,10 +11001,10 @@
     <row r="386" spans="1:11" ht="16.5">
       <c r="A386" s="4"/>
       <c r="B386" s="5" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="C386" s="6" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="D386" s="4"/>
       <c r="E386" s="6" t="s">
@@ -11019,10 +11020,10 @@
     <row r="387" spans="1:11" ht="16.5">
       <c r="A387" s="4"/>
       <c r="B387" s="5" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="C387" s="6" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="D387" s="4"/>
       <c r="E387" s="6" t="s">
@@ -11038,10 +11039,10 @@
     <row r="388" spans="1:11" ht="16.5">
       <c r="A388" s="4"/>
       <c r="B388" s="5" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="C388" s="6" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="D388" s="4"/>
       <c r="E388" s="6" t="s">
@@ -11057,10 +11058,10 @@
     <row r="389" spans="1:11" ht="16.5">
       <c r="A389" s="4"/>
       <c r="B389" s="5" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="C389" s="6" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="D389" s="4"/>
       <c r="E389" s="6" t="s">
@@ -11076,10 +11077,10 @@
     <row r="390" spans="1:11" ht="16.5">
       <c r="A390" s="4"/>
       <c r="B390" s="5" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="C390" s="6" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="D390" s="4"/>
       <c r="E390" s="6" t="s">
@@ -11095,10 +11096,10 @@
     <row r="391" spans="1:11" ht="16.5">
       <c r="A391" s="4"/>
       <c r="B391" s="5" t="s">
+        <v>687</v>
+      </c>
+      <c r="C391" s="6" t="s">
         <v>688</v>
-      </c>
-      <c r="C391" s="6" t="s">
-        <v>689</v>
       </c>
       <c r="D391" s="4"/>
       <c r="E391" s="6" t="s">
@@ -11114,10 +11115,10 @@
     <row r="392" spans="1:11" ht="16.5">
       <c r="A392" s="4"/>
       <c r="B392" s="5" t="s">
+        <v>689</v>
+      </c>
+      <c r="C392" s="6" t="s">
         <v>690</v>
-      </c>
-      <c r="C392" s="6" t="s">
-        <v>691</v>
       </c>
       <c r="D392" s="4"/>
       <c r="E392" s="6" t="s">
@@ -11133,10 +11134,10 @@
     <row r="393" spans="1:11" ht="16.5">
       <c r="A393" s="4"/>
       <c r="B393" s="5" t="s">
+        <v>691</v>
+      </c>
+      <c r="C393" s="6" t="s">
         <v>692</v>
-      </c>
-      <c r="C393" s="6" t="s">
-        <v>693</v>
       </c>
       <c r="D393" s="4"/>
       <c r="E393" s="6" t="s">

--- a/幽灵歌单整理.xlsx
+++ b/幽灵歌单整理.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Ksoftware\v-song-list-main\v-song-list9\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F21B369E-2028-4100-ACD6-F017FB557528}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07D8E30C-CCA6-42DF-91B1-70996DA76930}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="380" yWindow="380" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1571" uniqueCount="854">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1574" uniqueCount="857">
   <si>
     <t>价格</t>
   </si>
@@ -3168,6 +3168,18 @@
   </si>
   <si>
     <t>雨爱(remix)</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>像鱼</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>王贰浪</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>国语</t>
     <phoneticPr fontId="17" type="noConversion"/>
   </si>
 </sst>
@@ -3187,12 +3199,14 @@
     <font>
       <sz val="12"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF222222"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -3695,7 +3709,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1">
+  <sheetPr>
     <tabColor rgb="FFFFFFFF"/>
   </sheetPr>
   <dimension ref="A1:K490"/>
@@ -3735,7 +3749,7 @@
       <c r="J1" s="6"/>
       <c r="K1" s="6"/>
     </row>
-    <row r="2" spans="1:11" ht="15.5" hidden="1">
+    <row r="2" spans="1:11" ht="15.5">
       <c r="A2" s="1"/>
       <c r="B2" s="2" t="s">
         <v>17</v>
@@ -3754,7 +3768,7 @@
       <c r="J2" s="6"/>
       <c r="K2" s="6"/>
     </row>
-    <row r="3" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="3" spans="1:11" ht="18" customHeight="1">
       <c r="A3" s="1"/>
       <c r="B3" s="2" t="s">
         <v>19</v>
@@ -3775,7 +3789,7 @@
       <c r="J3" s="6"/>
       <c r="K3" s="6"/>
     </row>
-    <row r="4" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="4" spans="1:11" ht="18" customHeight="1">
       <c r="A4" s="6"/>
       <c r="B4" s="2" t="s">
         <v>22</v>
@@ -3796,7 +3810,7 @@
       <c r="J4" s="6"/>
       <c r="K4" s="6"/>
     </row>
-    <row r="5" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="5" spans="1:11" ht="18" customHeight="1">
       <c r="A5" s="6"/>
       <c r="B5" s="2" t="s">
         <v>24</v>
@@ -3815,7 +3829,7 @@
       <c r="J5" s="6"/>
       <c r="K5" s="6"/>
     </row>
-    <row r="6" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="6" spans="1:11" ht="18" customHeight="1">
       <c r="A6" s="6"/>
       <c r="B6" s="2" t="s">
         <v>26</v>
@@ -3834,7 +3848,7 @@
       <c r="J6" s="6"/>
       <c r="K6" s="6"/>
     </row>
-    <row r="7" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="7" spans="1:11" ht="18" customHeight="1">
       <c r="A7" s="6"/>
       <c r="B7" s="2" t="s">
         <v>28</v>
@@ -3855,7 +3869,7 @@
       <c r="J7" s="6"/>
       <c r="K7" s="6"/>
     </row>
-    <row r="8" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="8" spans="1:11" ht="18" customHeight="1">
       <c r="A8" s="1"/>
       <c r="B8" s="2" t="s">
         <v>30</v>
@@ -3874,7 +3888,7 @@
       <c r="J8" s="6"/>
       <c r="K8" s="6"/>
     </row>
-    <row r="9" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="9" spans="1:11" ht="18" customHeight="1">
       <c r="A9" s="6"/>
       <c r="B9" s="2" t="s">
         <v>31</v>
@@ -3893,7 +3907,7 @@
       <c r="J9" s="6"/>
       <c r="K9" s="6"/>
     </row>
-    <row r="10" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="10" spans="1:11" ht="18" customHeight="1">
       <c r="A10" s="6"/>
       <c r="B10" s="2" t="s">
         <v>33</v>
@@ -3914,7 +3928,7 @@
       <c r="J10" s="6"/>
       <c r="K10" s="6"/>
     </row>
-    <row r="11" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="11" spans="1:11" ht="18" customHeight="1">
       <c r="A11" s="1"/>
       <c r="B11" s="2" t="s">
         <v>35</v>
@@ -3933,7 +3947,7 @@
       <c r="J11" s="6"/>
       <c r="K11" s="6"/>
     </row>
-    <row r="12" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="12" spans="1:11" ht="18" customHeight="1">
       <c r="A12" s="6"/>
       <c r="B12" s="2" t="s">
         <v>37</v>
@@ -3952,7 +3966,7 @@
       <c r="J12" s="6"/>
       <c r="K12" s="6"/>
     </row>
-    <row r="13" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="13" spans="1:11" ht="18" customHeight="1">
       <c r="A13" s="6"/>
       <c r="B13" s="2" t="s">
         <v>38</v>
@@ -3971,7 +3985,7 @@
       <c r="J13" s="6"/>
       <c r="K13" s="6"/>
     </row>
-    <row r="14" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="14" spans="1:11" ht="18" customHeight="1">
       <c r="A14" s="6"/>
       <c r="B14" s="2" t="s">
         <v>39</v>
@@ -3990,7 +4004,7 @@
       <c r="J14" s="6"/>
       <c r="K14" s="6"/>
     </row>
-    <row r="15" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="15" spans="1:11" ht="18" customHeight="1">
       <c r="A15" s="6"/>
       <c r="B15" s="2" t="s">
         <v>40</v>
@@ -4009,7 +4023,7 @@
       <c r="J15" s="6"/>
       <c r="K15" s="6"/>
     </row>
-    <row r="16" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="16" spans="1:11" ht="18" customHeight="1">
       <c r="A16" s="6"/>
       <c r="B16" s="2" t="s">
         <v>41</v>
@@ -4030,7 +4044,7 @@
       <c r="J16" s="6"/>
       <c r="K16" s="6"/>
     </row>
-    <row r="17" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="17" spans="1:11" ht="18" customHeight="1">
       <c r="A17" s="6"/>
       <c r="B17" s="2" t="s">
         <v>42</v>
@@ -4049,7 +4063,7 @@
       <c r="J17" s="6"/>
       <c r="K17" s="6"/>
     </row>
-    <row r="18" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="18" spans="1:11" ht="18" customHeight="1">
       <c r="A18" s="6"/>
       <c r="B18" s="2" t="s">
         <v>43</v>
@@ -4068,7 +4082,7 @@
       <c r="J18" s="6"/>
       <c r="K18" s="6"/>
     </row>
-    <row r="19" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="19" spans="1:11" ht="18" customHeight="1">
       <c r="A19" s="6"/>
       <c r="B19" s="2" t="s">
         <v>44</v>
@@ -4087,7 +4101,7 @@
       <c r="J19" s="6"/>
       <c r="K19" s="6"/>
     </row>
-    <row r="20" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="20" spans="1:11" ht="18" customHeight="1">
       <c r="A20" s="6"/>
       <c r="B20" s="2" t="s">
         <v>45</v>
@@ -4108,7 +4122,7 @@
       <c r="J20" s="6"/>
       <c r="K20" s="6"/>
     </row>
-    <row r="21" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="21" spans="1:11" ht="18" customHeight="1">
       <c r="A21" s="6"/>
       <c r="B21" s="2" t="s">
         <v>46</v>
@@ -4127,7 +4141,7 @@
       <c r="J21" s="6"/>
       <c r="K21" s="6"/>
     </row>
-    <row r="22" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="22" spans="1:11" ht="18" customHeight="1">
       <c r="A22" s="1"/>
       <c r="B22" s="2" t="s">
         <v>48</v>
@@ -4146,7 +4160,7 @@
       <c r="J22" s="6"/>
       <c r="K22" s="6"/>
     </row>
-    <row r="23" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="23" spans="1:11" ht="18" customHeight="1">
       <c r="A23" s="6"/>
       <c r="B23" s="2" t="s">
         <v>50</v>
@@ -4165,7 +4179,7 @@
       <c r="J23" s="6"/>
       <c r="K23" s="6"/>
     </row>
-    <row r="24" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="24" spans="1:11" ht="18" customHeight="1">
       <c r="A24" s="6"/>
       <c r="B24" s="2" t="s">
         <v>52</v>
@@ -4184,7 +4198,7 @@
       <c r="J24" s="6"/>
       <c r="K24" s="6"/>
     </row>
-    <row r="25" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="25" spans="1:11" ht="18" customHeight="1">
       <c r="A25" s="6"/>
       <c r="B25" s="2" t="s">
         <v>53</v>
@@ -4203,7 +4217,7 @@
       <c r="J25" s="6"/>
       <c r="K25" s="6"/>
     </row>
-    <row r="26" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="26" spans="1:11" ht="18" customHeight="1">
       <c r="A26" s="6"/>
       <c r="B26" s="2" t="s">
         <v>54</v>
@@ -4222,7 +4236,7 @@
       <c r="J26" s="6"/>
       <c r="K26" s="6"/>
     </row>
-    <row r="27" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="27" spans="1:11" ht="18" customHeight="1">
       <c r="A27" s="6"/>
       <c r="B27" s="2" t="s">
         <v>55</v>
@@ -4243,7 +4257,7 @@
       <c r="J27" s="6"/>
       <c r="K27" s="6"/>
     </row>
-    <row r="28" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="28" spans="1:11" ht="18" customHeight="1">
       <c r="A28" s="6"/>
       <c r="B28" s="2" t="s">
         <v>57</v>
@@ -4264,7 +4278,7 @@
       <c r="J28" s="6"/>
       <c r="K28" s="6"/>
     </row>
-    <row r="29" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="29" spans="1:11" ht="18" customHeight="1">
       <c r="A29" s="6">
         <v>200</v>
       </c>
@@ -4285,7 +4299,7 @@
       <c r="J29" s="6"/>
       <c r="K29" s="6"/>
     </row>
-    <row r="30" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="30" spans="1:11" ht="18" customHeight="1">
       <c r="A30" s="6"/>
       <c r="B30" s="2" t="s">
         <v>62</v>
@@ -4304,7 +4318,7 @@
       <c r="J30" s="6"/>
       <c r="K30" s="6"/>
     </row>
-    <row r="31" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="31" spans="1:11" ht="18" customHeight="1">
       <c r="A31" s="6"/>
       <c r="B31" s="12" t="s">
         <v>65</v>
@@ -4323,7 +4337,7 @@
       <c r="J31" s="6"/>
       <c r="K31" s="6"/>
     </row>
-    <row r="32" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="32" spans="1:11" ht="18" customHeight="1">
       <c r="A32" s="1"/>
       <c r="B32" s="2" t="s">
         <v>67</v>
@@ -4342,7 +4356,7 @@
       <c r="J32" s="6"/>
       <c r="K32" s="6"/>
     </row>
-    <row r="33" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="33" spans="1:11" ht="18" customHeight="1">
       <c r="A33" s="1"/>
       <c r="B33" s="2" t="s">
         <v>69</v>
@@ -4361,7 +4375,7 @@
       <c r="J33" s="6"/>
       <c r="K33" s="6"/>
     </row>
-    <row r="34" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="34" spans="1:11" ht="18" customHeight="1">
       <c r="A34" s="6"/>
       <c r="B34" s="2" t="s">
         <v>71</v>
@@ -4380,7 +4394,7 @@
       <c r="J34" s="6"/>
       <c r="K34" s="6"/>
     </row>
-    <row r="35" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="35" spans="1:11" ht="18" customHeight="1">
       <c r="A35" s="6"/>
       <c r="B35" s="2" t="s">
         <v>73</v>
@@ -4399,7 +4413,7 @@
       <c r="J35" s="6"/>
       <c r="K35" s="6"/>
     </row>
-    <row r="36" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="36" spans="1:11" ht="18" customHeight="1">
       <c r="A36" s="6"/>
       <c r="B36" s="2" t="s">
         <v>75</v>
@@ -4420,7 +4434,7 @@
       <c r="J36" s="6"/>
       <c r="K36" s="6"/>
     </row>
-    <row r="37" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="37" spans="1:11" ht="18" customHeight="1">
       <c r="A37" s="1"/>
       <c r="B37" s="2" t="s">
         <v>77</v>
@@ -4441,7 +4455,7 @@
       <c r="J37" s="6"/>
       <c r="K37" s="6"/>
     </row>
-    <row r="38" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="38" spans="1:11" ht="18" customHeight="1">
       <c r="A38" s="1"/>
       <c r="B38" s="2" t="s">
         <v>79</v>
@@ -4462,7 +4476,7 @@
       <c r="J38" s="6"/>
       <c r="K38" s="6"/>
     </row>
-    <row r="39" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="39" spans="1:11" ht="18" customHeight="1">
       <c r="A39" s="1"/>
       <c r="B39" s="12" t="s">
         <v>80</v>
@@ -4483,7 +4497,7 @@
       <c r="J39" s="6"/>
       <c r="K39" s="6"/>
     </row>
-    <row r="40" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="40" spans="1:11" ht="18" customHeight="1">
       <c r="A40" s="6"/>
       <c r="B40" s="2" t="s">
         <v>81</v>
@@ -4502,7 +4516,7 @@
       <c r="J40" s="6"/>
       <c r="K40" s="6"/>
     </row>
-    <row r="41" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="41" spans="1:11" ht="18" customHeight="1">
       <c r="A41" s="6"/>
       <c r="B41" s="2" t="s">
         <v>83</v>
@@ -4521,7 +4535,7 @@
       <c r="J41" s="6"/>
       <c r="K41" s="6"/>
     </row>
-    <row r="42" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="42" spans="1:11" ht="18" customHeight="1">
       <c r="A42" s="6"/>
       <c r="B42" s="2" t="s">
         <v>85</v>
@@ -4540,7 +4554,7 @@
       <c r="J42" s="6"/>
       <c r="K42" s="6"/>
     </row>
-    <row r="43" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="43" spans="1:11" ht="18" customHeight="1">
       <c r="A43" s="6"/>
       <c r="B43" s="2" t="s">
         <v>86</v>
@@ -4559,7 +4573,7 @@
       <c r="J43" s="6"/>
       <c r="K43" s="6"/>
     </row>
-    <row r="44" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="44" spans="1:11" ht="18" customHeight="1">
       <c r="A44" s="6"/>
       <c r="B44" s="2" t="s">
         <v>87</v>
@@ -4578,7 +4592,7 @@
       <c r="J44" s="6"/>
       <c r="K44" s="6"/>
     </row>
-    <row r="45" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="45" spans="1:11" ht="18" customHeight="1">
       <c r="A45" s="6"/>
       <c r="B45" s="2" t="s">
         <v>89</v>
@@ -4597,7 +4611,7 @@
       <c r="J45" s="6"/>
       <c r="K45" s="6"/>
     </row>
-    <row r="46" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="46" spans="1:11" ht="18" customHeight="1">
       <c r="A46" s="1"/>
       <c r="B46" s="2" t="s">
         <v>91</v>
@@ -4616,7 +4630,7 @@
       <c r="J46" s="6"/>
       <c r="K46" s="6"/>
     </row>
-    <row r="47" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="47" spans="1:11" ht="18" customHeight="1">
       <c r="A47" s="1"/>
       <c r="B47" s="2" t="s">
         <v>92</v>
@@ -4635,7 +4649,7 @@
       <c r="J47" s="6"/>
       <c r="K47" s="6"/>
     </row>
-    <row r="48" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="48" spans="1:11" ht="18" customHeight="1">
       <c r="A48" s="1"/>
       <c r="B48" s="2" t="s">
         <v>93</v>
@@ -4654,7 +4668,7 @@
       <c r="J48" s="6"/>
       <c r="K48" s="6"/>
     </row>
-    <row r="49" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="49" spans="1:11" ht="18" customHeight="1">
       <c r="A49" s="1"/>
       <c r="B49" s="2" t="s">
         <v>94</v>
@@ -4673,7 +4687,7 @@
       <c r="J49" s="6"/>
       <c r="K49" s="6"/>
     </row>
-    <row r="50" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="50" spans="1:11" ht="18" customHeight="1">
       <c r="A50" s="6"/>
       <c r="B50" s="2" t="s">
         <v>95</v>
@@ -4696,7 +4710,7 @@
       <c r="J50" s="6"/>
       <c r="K50" s="6"/>
     </row>
-    <row r="51" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="51" spans="1:11" ht="18" customHeight="1">
       <c r="A51" s="1"/>
       <c r="B51" s="2" t="s">
         <v>97</v>
@@ -4715,7 +4729,7 @@
       <c r="J51" s="6"/>
       <c r="K51" s="6"/>
     </row>
-    <row r="52" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="52" spans="1:11" ht="18" customHeight="1">
       <c r="A52" s="1"/>
       <c r="B52" s="2" t="s">
         <v>98</v>
@@ -4734,7 +4748,7 @@
       <c r="J52" s="6"/>
       <c r="K52" s="6"/>
     </row>
-    <row r="53" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="53" spans="1:11" ht="18" customHeight="1">
       <c r="A53" s="1"/>
       <c r="B53" s="2" t="s">
         <v>99</v>
@@ -4753,7 +4767,7 @@
       <c r="J53" s="6"/>
       <c r="K53" s="6"/>
     </row>
-    <row r="54" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="54" spans="1:11" ht="18" customHeight="1">
       <c r="A54" s="1"/>
       <c r="B54" s="2" t="s">
         <v>100</v>
@@ -4772,7 +4786,7 @@
       <c r="J54" s="6"/>
       <c r="K54" s="6"/>
     </row>
-    <row r="55" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="55" spans="1:11" ht="18" customHeight="1">
       <c r="A55" s="1"/>
       <c r="B55" s="2" t="s">
         <v>101</v>
@@ -4791,7 +4805,7 @@
       <c r="J55" s="6"/>
       <c r="K55" s="6"/>
     </row>
-    <row r="56" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="56" spans="1:11" ht="18" customHeight="1">
       <c r="A56" s="1"/>
       <c r="B56" s="2" t="s">
         <v>102</v>
@@ -4810,7 +4824,7 @@
       <c r="J56" s="6"/>
       <c r="K56" s="6"/>
     </row>
-    <row r="57" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="57" spans="1:11" ht="18" customHeight="1">
       <c r="A57" s="1"/>
       <c r="B57" s="2" t="s">
         <v>103</v>
@@ -4829,7 +4843,7 @@
       <c r="J57" s="6"/>
       <c r="K57" s="6"/>
     </row>
-    <row r="58" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="58" spans="1:11" ht="18" customHeight="1">
       <c r="A58" s="1"/>
       <c r="B58" s="2" t="s">
         <v>104</v>
@@ -4848,7 +4862,7 @@
       <c r="J58" s="6"/>
       <c r="K58" s="6"/>
     </row>
-    <row r="59" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="59" spans="1:11" ht="18" customHeight="1">
       <c r="A59" s="1"/>
       <c r="B59" s="2" t="s">
         <v>105</v>
@@ -4867,7 +4881,7 @@
       <c r="J59" s="6"/>
       <c r="K59" s="6"/>
     </row>
-    <row r="60" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="60" spans="1:11" ht="18" customHeight="1">
       <c r="A60" s="1"/>
       <c r="B60" s="2" t="s">
         <v>106</v>
@@ -4886,7 +4900,7 @@
       <c r="J60" s="6"/>
       <c r="K60" s="6"/>
     </row>
-    <row r="61" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="61" spans="1:11" ht="18" customHeight="1">
       <c r="A61" s="1"/>
       <c r="B61" s="2" t="s">
         <v>107</v>
@@ -4905,7 +4919,7 @@
       <c r="J61" s="6"/>
       <c r="K61" s="6"/>
     </row>
-    <row r="62" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="62" spans="1:11" ht="18" customHeight="1">
       <c r="A62" s="1"/>
       <c r="B62" s="2" t="s">
         <v>108</v>
@@ -4926,7 +4940,7 @@
       <c r="J62" s="6"/>
       <c r="K62" s="6"/>
     </row>
-    <row r="63" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="63" spans="1:11" ht="18" customHeight="1">
       <c r="A63" s="6"/>
       <c r="B63" s="2" t="s">
         <v>111</v>
@@ -4945,7 +4959,7 @@
       <c r="J63" s="6"/>
       <c r="K63" s="6"/>
     </row>
-    <row r="64" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="64" spans="1:11" ht="18" customHeight="1">
       <c r="A64" s="1"/>
       <c r="B64" s="2" t="s">
         <v>113</v>
@@ -4964,7 +4978,7 @@
       <c r="J64" s="6"/>
       <c r="K64" s="6"/>
     </row>
-    <row r="65" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="65" spans="1:11" ht="18" customHeight="1">
       <c r="A65" s="6"/>
       <c r="B65" s="2" t="s">
         <v>115</v>
@@ -4983,7 +4997,7 @@
       <c r="J65" s="6"/>
       <c r="K65" s="6"/>
     </row>
-    <row r="66" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="66" spans="1:11" ht="18" customHeight="1">
       <c r="A66" s="6"/>
       <c r="B66" s="2" t="s">
         <v>117</v>
@@ -5002,7 +5016,7 @@
       <c r="J66" s="6"/>
       <c r="K66" s="6"/>
     </row>
-    <row r="67" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="67" spans="1:11" ht="18" customHeight="1">
       <c r="A67" s="1"/>
       <c r="B67" s="2" t="s">
         <v>119</v>
@@ -5021,7 +5035,7 @@
       <c r="J67" s="6"/>
       <c r="K67" s="6"/>
     </row>
-    <row r="68" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="68" spans="1:11" ht="18" customHeight="1">
       <c r="A68" s="6"/>
       <c r="B68" s="2" t="s">
         <v>121</v>
@@ -5040,7 +5054,7 @@
       <c r="J68" s="6"/>
       <c r="K68" s="6"/>
     </row>
-    <row r="69" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="69" spans="1:11" ht="18" customHeight="1">
       <c r="A69" s="1"/>
       <c r="B69" s="2" t="s">
         <v>124</v>
@@ -5061,7 +5075,7 @@
       <c r="J69" s="6"/>
       <c r="K69" s="6"/>
     </row>
-    <row r="70" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="70" spans="1:11" ht="18" customHeight="1">
       <c r="A70" s="1"/>
       <c r="B70" s="2" t="s">
         <v>126</v>
@@ -5080,7 +5094,7 @@
       <c r="J70" s="6"/>
       <c r="K70" s="6"/>
     </row>
-    <row r="71" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="71" spans="1:11" ht="18" customHeight="1">
       <c r="A71" s="6"/>
       <c r="B71" s="2" t="s">
         <v>127</v>
@@ -5099,7 +5113,7 @@
       <c r="J71" s="6"/>
       <c r="K71" s="6"/>
     </row>
-    <row r="72" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="72" spans="1:11" ht="18" customHeight="1">
       <c r="A72" s="6"/>
       <c r="B72" s="2" t="s">
         <v>128</v>
@@ -5118,7 +5132,7 @@
       <c r="J72" s="6"/>
       <c r="K72" s="6"/>
     </row>
-    <row r="73" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="73" spans="1:11" ht="18" customHeight="1">
       <c r="A73" s="6"/>
       <c r="B73" s="2" t="s">
         <v>129</v>
@@ -5137,7 +5151,7 @@
       <c r="J73" s="6"/>
       <c r="K73" s="6"/>
     </row>
-    <row r="74" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="74" spans="1:11" ht="18" customHeight="1">
       <c r="A74" s="1"/>
       <c r="B74" s="2" t="s">
         <v>130</v>
@@ -5158,7 +5172,7 @@
       <c r="J74" s="6"/>
       <c r="K74" s="6"/>
     </row>
-    <row r="75" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="75" spans="1:11" ht="18" customHeight="1">
       <c r="A75" s="1"/>
       <c r="B75" s="2" t="s">
         <v>133</v>
@@ -5179,7 +5193,7 @@
       <c r="J75" s="6"/>
       <c r="K75" s="6"/>
     </row>
-    <row r="76" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="76" spans="1:11" ht="18" customHeight="1">
       <c r="A76" s="1"/>
       <c r="B76" s="2" t="s">
         <v>134</v>
@@ -5198,7 +5212,7 @@
       <c r="J76" s="6"/>
       <c r="K76" s="6"/>
     </row>
-    <row r="77" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="77" spans="1:11" ht="18" customHeight="1">
       <c r="A77" s="1"/>
       <c r="B77" s="2" t="s">
         <v>135</v>
@@ -5219,7 +5233,7 @@
       <c r="J77" s="6"/>
       <c r="K77" s="6"/>
     </row>
-    <row r="78" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="78" spans="1:11" ht="18" customHeight="1">
       <c r="A78" s="1"/>
       <c r="B78" s="2" t="s">
         <v>136</v>
@@ -5240,7 +5254,7 @@
       <c r="J78" s="6"/>
       <c r="K78" s="6"/>
     </row>
-    <row r="79" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="79" spans="1:11" ht="18" customHeight="1">
       <c r="A79" s="1"/>
       <c r="B79" s="2" t="s">
         <v>137</v>
@@ -5261,7 +5275,7 @@
       <c r="J79" s="6"/>
       <c r="K79" s="6"/>
     </row>
-    <row r="80" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="80" spans="1:11" ht="18" customHeight="1">
       <c r="A80" s="1"/>
       <c r="B80" s="2" t="s">
         <v>138</v>
@@ -5282,7 +5296,7 @@
       <c r="J80" s="6"/>
       <c r="K80" s="6"/>
     </row>
-    <row r="81" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="81" spans="1:11" ht="18" customHeight="1">
       <c r="A81" s="1"/>
       <c r="B81" s="2" t="s">
         <v>139</v>
@@ -5303,7 +5317,7 @@
       <c r="J81" s="6"/>
       <c r="K81" s="6"/>
     </row>
-    <row r="82" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="82" spans="1:11" ht="18" customHeight="1">
       <c r="A82" s="6"/>
       <c r="B82" s="2" t="s">
         <v>140</v>
@@ -5324,7 +5338,7 @@
       <c r="J82" s="6"/>
       <c r="K82" s="6"/>
     </row>
-    <row r="83" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="83" spans="1:11" ht="18" customHeight="1">
       <c r="A83" s="1"/>
       <c r="B83" s="2" t="s">
         <v>141</v>
@@ -5345,7 +5359,7 @@
       <c r="J83" s="6"/>
       <c r="K83" s="6"/>
     </row>
-    <row r="84" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="84" spans="1:11" ht="18" customHeight="1">
       <c r="A84" s="1"/>
       <c r="B84" s="2" t="s">
         <v>142</v>
@@ -5366,7 +5380,7 @@
       <c r="J84" s="6"/>
       <c r="K84" s="6"/>
     </row>
-    <row r="85" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="85" spans="1:11" ht="18" customHeight="1">
       <c r="A85" s="1"/>
       <c r="B85" s="2" t="s">
         <v>143</v>
@@ -5387,7 +5401,7 @@
       <c r="J85" s="6"/>
       <c r="K85" s="6"/>
     </row>
-    <row r="86" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="86" spans="1:11" ht="18" customHeight="1">
       <c r="A86" s="6"/>
       <c r="B86" s="2" t="s">
         <v>144</v>
@@ -5406,7 +5420,7 @@
       <c r="J86" s="6"/>
       <c r="K86" s="6"/>
     </row>
-    <row r="87" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="87" spans="1:11" ht="18" customHeight="1">
       <c r="A87" s="6"/>
       <c r="B87" s="2" t="s">
         <v>146</v>
@@ -5429,7 +5443,7 @@
       <c r="J87" s="6"/>
       <c r="K87" s="6"/>
     </row>
-    <row r="88" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="88" spans="1:11" ht="18" customHeight="1">
       <c r="A88" s="6"/>
       <c r="B88" s="2" t="s">
         <v>148</v>
@@ -5450,7 +5464,7 @@
       <c r="J88" s="6"/>
       <c r="K88" s="6"/>
     </row>
-    <row r="89" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="89" spans="1:11" ht="18" customHeight="1">
       <c r="A89" s="6"/>
       <c r="B89" s="2" t="s">
         <v>151</v>
@@ -5469,7 +5483,7 @@
       <c r="J89" s="6"/>
       <c r="K89" s="6"/>
     </row>
-    <row r="90" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="90" spans="1:11" ht="18" customHeight="1">
       <c r="A90" s="6"/>
       <c r="B90" s="2" t="s">
         <v>153</v>
@@ -5490,7 +5504,7 @@
       <c r="J90" s="6"/>
       <c r="K90" s="6"/>
     </row>
-    <row r="91" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="91" spans="1:11" ht="18" customHeight="1">
       <c r="A91" s="1"/>
       <c r="B91" s="2" t="s">
         <v>155</v>
@@ -5511,7 +5525,7 @@
       <c r="J91" s="6"/>
       <c r="K91" s="6"/>
     </row>
-    <row r="92" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="92" spans="1:11" ht="18" customHeight="1">
       <c r="A92" s="1"/>
       <c r="B92" s="2" t="s">
         <v>158</v>
@@ -5530,7 +5544,7 @@
       <c r="J92" s="6"/>
       <c r="K92" s="6"/>
     </row>
-    <row r="93" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="93" spans="1:11" ht="18" customHeight="1">
       <c r="A93" s="6"/>
       <c r="B93" s="12" t="s">
         <v>161</v>
@@ -5549,7 +5563,7 @@
       <c r="J93" s="6"/>
       <c r="K93" s="6"/>
     </row>
-    <row r="94" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="94" spans="1:11" ht="18" customHeight="1">
       <c r="A94" s="6"/>
       <c r="B94" s="2" t="s">
         <v>163</v>
@@ -5568,7 +5582,7 @@
       <c r="J94" s="6"/>
       <c r="K94" s="6"/>
     </row>
-    <row r="95" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="95" spans="1:11" ht="18" customHeight="1">
       <c r="A95" s="6"/>
       <c r="B95" s="2" t="s">
         <v>165</v>
@@ -5587,7 +5601,7 @@
       <c r="J95" s="6"/>
       <c r="K95" s="6"/>
     </row>
-    <row r="96" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="96" spans="1:11" ht="18" customHeight="1">
       <c r="A96" s="6"/>
       <c r="B96" s="2" t="s">
         <v>167</v>
@@ -5606,7 +5620,7 @@
       <c r="J96" s="6"/>
       <c r="K96" s="6"/>
     </row>
-    <row r="97" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="97" spans="1:11" ht="18" customHeight="1">
       <c r="A97" s="6"/>
       <c r="B97" s="2" t="s">
         <v>168</v>
@@ -5625,7 +5639,7 @@
       <c r="J97" s="6"/>
       <c r="K97" s="6"/>
     </row>
-    <row r="98" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="98" spans="1:11" ht="18" customHeight="1">
       <c r="A98" s="6"/>
       <c r="B98" s="2" t="s">
         <v>170</v>
@@ -5644,7 +5658,7 @@
       <c r="J98" s="6"/>
       <c r="K98" s="6"/>
     </row>
-    <row r="99" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="99" spans="1:11" ht="18" customHeight="1">
       <c r="A99" s="6"/>
       <c r="B99" s="2" t="s">
         <v>172</v>
@@ -5663,7 +5677,7 @@
       <c r="J99" s="6"/>
       <c r="K99" s="6"/>
     </row>
-    <row r="100" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="100" spans="1:11" ht="18" customHeight="1">
       <c r="A100" s="6"/>
       <c r="B100" s="2" t="s">
         <v>174</v>
@@ -5684,7 +5698,7 @@
       <c r="J100" s="6"/>
       <c r="K100" s="6"/>
     </row>
-    <row r="101" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="101" spans="1:11" ht="18" customHeight="1">
       <c r="A101" s="1"/>
       <c r="B101" s="2" t="s">
         <v>177</v>
@@ -5703,7 +5717,7 @@
       <c r="J101" s="6"/>
       <c r="K101" s="6"/>
     </row>
-    <row r="102" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="102" spans="1:11" ht="18" customHeight="1">
       <c r="A102" s="6"/>
       <c r="B102" s="2" t="s">
         <v>179</v>
@@ -5722,7 +5736,7 @@
       <c r="J102" s="6"/>
       <c r="K102" s="6"/>
     </row>
-    <row r="103" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="103" spans="1:11" ht="18" customHeight="1">
       <c r="A103" s="1"/>
       <c r="B103" s="2" t="s">
         <v>181</v>
@@ -5741,7 +5755,7 @@
       <c r="J103" s="6"/>
       <c r="K103" s="6"/>
     </row>
-    <row r="104" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="104" spans="1:11" ht="18" customHeight="1">
       <c r="A104" s="6"/>
       <c r="B104" s="2" t="s">
         <v>183</v>
@@ -5760,7 +5774,7 @@
       <c r="J104" s="6"/>
       <c r="K104" s="6"/>
     </row>
-    <row r="105" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="105" spans="1:11" ht="18" customHeight="1">
       <c r="A105" s="6"/>
       <c r="B105" s="2" t="s">
         <v>184</v>
@@ -5779,7 +5793,7 @@
       <c r="J105" s="6"/>
       <c r="K105" s="6"/>
     </row>
-    <row r="106" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="106" spans="1:11" ht="18" customHeight="1">
       <c r="A106" s="6"/>
       <c r="B106" s="2" t="s">
         <v>185</v>
@@ -5798,7 +5812,7 @@
       <c r="J106" s="6"/>
       <c r="K106" s="6"/>
     </row>
-    <row r="107" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="107" spans="1:11" ht="18" customHeight="1">
       <c r="A107" s="6"/>
       <c r="B107" s="2" t="s">
         <v>187</v>
@@ -5817,7 +5831,7 @@
       <c r="J107" s="6"/>
       <c r="K107" s="6"/>
     </row>
-    <row r="108" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="108" spans="1:11" ht="18" customHeight="1">
       <c r="A108" s="6"/>
       <c r="B108" s="2" t="s">
         <v>189</v>
@@ -5836,7 +5850,7 @@
       <c r="J108" s="6"/>
       <c r="K108" s="6"/>
     </row>
-    <row r="109" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="109" spans="1:11" ht="18" customHeight="1">
       <c r="A109" s="6"/>
       <c r="B109" s="2" t="s">
         <v>190</v>
@@ -5855,7 +5869,7 @@
       <c r="J109" s="6"/>
       <c r="K109" s="6"/>
     </row>
-    <row r="110" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="110" spans="1:11" ht="18" customHeight="1">
       <c r="A110" s="1"/>
       <c r="B110" s="2" t="s">
         <v>191</v>
@@ -5874,7 +5888,7 @@
       <c r="J110" s="6"/>
       <c r="K110" s="6"/>
     </row>
-    <row r="111" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="111" spans="1:11" ht="18" customHeight="1">
       <c r="A111" s="1"/>
       <c r="B111" s="2" t="s">
         <v>193</v>
@@ -5895,7 +5909,7 @@
       <c r="J111" s="6"/>
       <c r="K111" s="6"/>
     </row>
-    <row r="112" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="112" spans="1:11" ht="18" customHeight="1">
       <c r="A112" s="6"/>
       <c r="B112" s="2" t="s">
         <v>196</v>
@@ -5916,7 +5930,7 @@
       <c r="J112" s="6"/>
       <c r="K112" s="6"/>
     </row>
-    <row r="113" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="113" spans="1:11" ht="18" customHeight="1">
       <c r="A113" s="6"/>
       <c r="B113" s="2" t="s">
         <v>198</v>
@@ -5935,7 +5949,7 @@
       <c r="J113" s="6"/>
       <c r="K113" s="6"/>
     </row>
-    <row r="114" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="114" spans="1:11" ht="18" customHeight="1">
       <c r="A114" s="1"/>
       <c r="B114" s="2" t="s">
         <v>200</v>
@@ -5954,7 +5968,7 @@
       <c r="J114" s="6"/>
       <c r="K114" s="6"/>
     </row>
-    <row r="115" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="115" spans="1:11" ht="18" customHeight="1">
       <c r="A115" s="6"/>
       <c r="B115" s="2" t="s">
         <v>202</v>
@@ -5977,7 +5991,7 @@
       <c r="J115" s="6"/>
       <c r="K115" s="6"/>
     </row>
-    <row r="116" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="116" spans="1:11" ht="18" customHeight="1">
       <c r="A116" s="6"/>
       <c r="B116" s="2" t="s">
         <v>205</v>
@@ -5996,7 +6010,7 @@
       <c r="J116" s="6"/>
       <c r="K116" s="6"/>
     </row>
-    <row r="117" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="117" spans="1:11" ht="18" customHeight="1">
       <c r="A117" s="6"/>
       <c r="B117" s="2" t="s">
         <v>207</v>
@@ -6015,7 +6029,7 @@
       <c r="J117" s="6"/>
       <c r="K117" s="6"/>
     </row>
-    <row r="118" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="118" spans="1:11" ht="18" customHeight="1">
       <c r="A118" s="6"/>
       <c r="B118" s="2" t="s">
         <v>209</v>
@@ -6034,7 +6048,7 @@
       <c r="J118" s="6"/>
       <c r="K118" s="6"/>
     </row>
-    <row r="119" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="119" spans="1:11" ht="18" customHeight="1">
       <c r="A119" s="6"/>
       <c r="B119" s="2" t="s">
         <v>210</v>
@@ -6053,7 +6067,7 @@
       <c r="J119" s="6"/>
       <c r="K119" s="6"/>
     </row>
-    <row r="120" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="120" spans="1:11" ht="18" customHeight="1">
       <c r="A120" s="6"/>
       <c r="B120" s="2" t="s">
         <v>211</v>
@@ -6072,7 +6086,7 @@
       <c r="J120" s="6"/>
       <c r="K120" s="6"/>
     </row>
-    <row r="121" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="121" spans="1:11" ht="18" customHeight="1">
       <c r="A121" s="6"/>
       <c r="B121" s="2" t="s">
         <v>212</v>
@@ -6091,7 +6105,7 @@
       <c r="J121" s="6"/>
       <c r="K121" s="6"/>
     </row>
-    <row r="122" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="122" spans="1:11" ht="18" customHeight="1">
       <c r="A122" s="6"/>
       <c r="B122" s="2" t="s">
         <v>214</v>
@@ -6110,7 +6124,7 @@
       <c r="J122" s="6"/>
       <c r="K122" s="6"/>
     </row>
-    <row r="123" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="123" spans="1:11" ht="18" customHeight="1">
       <c r="A123" s="6"/>
       <c r="B123" s="2" t="s">
         <v>215</v>
@@ -6129,7 +6143,7 @@
       <c r="J123" s="6"/>
       <c r="K123" s="6"/>
     </row>
-    <row r="124" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="124" spans="1:11" ht="18" customHeight="1">
       <c r="A124" s="6"/>
       <c r="B124" s="2" t="s">
         <v>217</v>
@@ -6148,7 +6162,7 @@
       <c r="J124" s="6"/>
       <c r="K124" s="6"/>
     </row>
-    <row r="125" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="125" spans="1:11" ht="18" customHeight="1">
       <c r="A125" s="6"/>
       <c r="B125" s="2" t="s">
         <v>218</v>
@@ -6167,7 +6181,7 @@
       <c r="J125" s="6"/>
       <c r="K125" s="6"/>
     </row>
-    <row r="126" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="126" spans="1:11" ht="18" customHeight="1">
       <c r="A126" s="6"/>
       <c r="B126" s="2" t="s">
         <v>219</v>
@@ -6186,7 +6200,7 @@
       <c r="J126" s="6"/>
       <c r="K126" s="6"/>
     </row>
-    <row r="127" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="127" spans="1:11" ht="18" customHeight="1">
       <c r="A127" s="6"/>
       <c r="B127" s="2" t="s">
         <v>221</v>
@@ -6205,7 +6219,7 @@
       <c r="J127" s="6"/>
       <c r="K127" s="6"/>
     </row>
-    <row r="128" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="128" spans="1:11" ht="18" customHeight="1">
       <c r="A128" s="6"/>
       <c r="B128" s="2" t="s">
         <v>223</v>
@@ -6224,7 +6238,7 @@
       <c r="J128" s="6"/>
       <c r="K128" s="6"/>
     </row>
-    <row r="129" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="129" spans="1:11" ht="18" customHeight="1">
       <c r="A129" s="6"/>
       <c r="B129" s="2" t="s">
         <v>225</v>
@@ -6245,7 +6259,7 @@
       <c r="J129" s="6"/>
       <c r="K129" s="6"/>
     </row>
-    <row r="130" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="130" spans="1:11" ht="18" customHeight="1">
       <c r="A130" s="6"/>
       <c r="B130" s="2" t="s">
         <v>226</v>
@@ -6266,7 +6280,7 @@
       <c r="J130" s="6"/>
       <c r="K130" s="6"/>
     </row>
-    <row r="131" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="131" spans="1:11" ht="18" customHeight="1">
       <c r="A131" s="1"/>
       <c r="B131" s="2" t="s">
         <v>228</v>
@@ -6285,7 +6299,7 @@
       <c r="J131" s="6"/>
       <c r="K131" s="6"/>
     </row>
-    <row r="132" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="132" spans="1:11" ht="18" customHeight="1">
       <c r="A132" s="6"/>
       <c r="B132" s="2" t="s">
         <v>230</v>
@@ -6304,7 +6318,7 @@
       <c r="J132" s="6"/>
       <c r="K132" s="6"/>
     </row>
-    <row r="133" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="133" spans="1:11" ht="18" customHeight="1">
       <c r="A133" s="6"/>
       <c r="B133" s="2" t="s">
         <v>231</v>
@@ -6323,7 +6337,7 @@
       <c r="J133" s="6"/>
       <c r="K133" s="6"/>
     </row>
-    <row r="134" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="134" spans="1:11" ht="18" customHeight="1">
       <c r="A134" s="6"/>
       <c r="B134" s="2" t="s">
         <v>232</v>
@@ -6344,7 +6358,7 @@
       <c r="J134" s="6"/>
       <c r="K134" s="6"/>
     </row>
-    <row r="135" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="135" spans="1:11" ht="18" customHeight="1">
       <c r="A135" s="6"/>
       <c r="B135" s="2" t="s">
         <v>233</v>
@@ -6365,7 +6379,7 @@
       <c r="J135" s="6"/>
       <c r="K135" s="6"/>
     </row>
-    <row r="136" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="136" spans="1:11" ht="18" customHeight="1">
       <c r="A136" s="6"/>
       <c r="B136" s="2" t="s">
         <v>234</v>
@@ -6384,7 +6398,7 @@
       <c r="J136" s="6"/>
       <c r="K136" s="6"/>
     </row>
-    <row r="137" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="137" spans="1:11" ht="18" customHeight="1">
       <c r="A137" s="6"/>
       <c r="B137" s="2" t="s">
         <v>236</v>
@@ -6403,7 +6417,7 @@
       <c r="J137" s="6"/>
       <c r="K137" s="6"/>
     </row>
-    <row r="138" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="138" spans="1:11" ht="18" customHeight="1">
       <c r="A138" s="6"/>
       <c r="B138" s="2" t="s">
         <v>238</v>
@@ -6424,7 +6438,7 @@
       <c r="J138" s="6"/>
       <c r="K138" s="6"/>
     </row>
-    <row r="139" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="139" spans="1:11" ht="18" customHeight="1">
       <c r="A139" s="1"/>
       <c r="B139" s="2" t="s">
         <v>240</v>
@@ -6443,7 +6457,7 @@
       <c r="J139" s="6"/>
       <c r="K139" s="6"/>
     </row>
-    <row r="140" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="140" spans="1:11" ht="18" customHeight="1">
       <c r="A140" s="6"/>
       <c r="B140" s="2" t="s">
         <v>242</v>
@@ -6462,7 +6476,7 @@
       <c r="J140" s="6"/>
       <c r="K140" s="6"/>
     </row>
-    <row r="141" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="141" spans="1:11" ht="18" customHeight="1">
       <c r="A141" s="1"/>
       <c r="B141" s="2" t="s">
         <v>244</v>
@@ -6481,7 +6495,7 @@
       <c r="J141" s="6"/>
       <c r="K141" s="6"/>
     </row>
-    <row r="142" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="142" spans="1:11" ht="18" customHeight="1">
       <c r="A142" s="1"/>
       <c r="B142" s="2" t="s">
         <v>246</v>
@@ -6502,7 +6516,7 @@
       <c r="J142" s="6"/>
       <c r="K142" s="6"/>
     </row>
-    <row r="143" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="143" spans="1:11" ht="18" customHeight="1">
       <c r="A143" s="6"/>
       <c r="B143" s="2" t="s">
         <v>249</v>
@@ -6521,7 +6535,7 @@
       <c r="J143" s="6"/>
       <c r="K143" s="6"/>
     </row>
-    <row r="144" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="144" spans="1:11" ht="18" customHeight="1">
       <c r="A144" s="1"/>
       <c r="B144" s="2" t="s">
         <v>250</v>
@@ -6540,7 +6554,7 @@
       <c r="J144" s="6"/>
       <c r="K144" s="6"/>
     </row>
-    <row r="145" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="145" spans="1:11" ht="18" customHeight="1">
       <c r="A145" s="6"/>
       <c r="B145" s="2" t="s">
         <v>251</v>
@@ -6559,7 +6573,7 @@
       <c r="J145" s="6"/>
       <c r="K145" s="6"/>
     </row>
-    <row r="146" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="146" spans="1:11" ht="18" customHeight="1">
       <c r="A146" s="1"/>
       <c r="B146" s="2" t="s">
         <v>253</v>
@@ -6578,7 +6592,7 @@
       <c r="J146" s="6"/>
       <c r="K146" s="6"/>
     </row>
-    <row r="147" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="147" spans="1:11" ht="18" customHeight="1">
       <c r="A147" s="6"/>
       <c r="B147" s="2" t="s">
         <v>254</v>
@@ -6597,7 +6611,7 @@
       <c r="J147" s="6"/>
       <c r="K147" s="6"/>
     </row>
-    <row r="148" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="148" spans="1:11" ht="18" customHeight="1">
       <c r="A148" s="6"/>
       <c r="B148" s="2" t="s">
         <v>255</v>
@@ -6616,7 +6630,7 @@
       <c r="J148" s="6"/>
       <c r="K148" s="6"/>
     </row>
-    <row r="149" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="149" spans="1:11" ht="18" customHeight="1">
       <c r="A149" s="6"/>
       <c r="B149" s="2" t="s">
         <v>257</v>
@@ -6635,7 +6649,7 @@
       <c r="J149" s="6"/>
       <c r="K149" s="6"/>
     </row>
-    <row r="150" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="150" spans="1:11" ht="18" customHeight="1">
       <c r="A150" s="6"/>
       <c r="B150" s="2" t="s">
         <v>258</v>
@@ -6654,7 +6668,7 @@
       <c r="J150" s="6"/>
       <c r="K150" s="6"/>
     </row>
-    <row r="151" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="151" spans="1:11" ht="18" customHeight="1">
       <c r="A151" s="1"/>
       <c r="B151" s="2" t="s">
         <v>259</v>
@@ -6673,7 +6687,7 @@
       <c r="J151" s="6"/>
       <c r="K151" s="6"/>
     </row>
-    <row r="152" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="152" spans="1:11" ht="18" customHeight="1">
       <c r="A152" s="6"/>
       <c r="B152" s="2" t="s">
         <v>261</v>
@@ -6694,7 +6708,7 @@
       <c r="J152" s="6"/>
       <c r="K152" s="6"/>
     </row>
-    <row r="153" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="153" spans="1:11" ht="18" customHeight="1">
       <c r="A153" s="6"/>
       <c r="B153" s="2" t="s">
         <v>263</v>
@@ -6717,7 +6731,7 @@
       <c r="J153" s="6"/>
       <c r="K153" s="6"/>
     </row>
-    <row r="154" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="154" spans="1:11" ht="18" customHeight="1">
       <c r="A154" s="6"/>
       <c r="B154" s="2" t="s">
         <v>266</v>
@@ -6738,7 +6752,7 @@
       <c r="J154" s="6"/>
       <c r="K154" s="6"/>
     </row>
-    <row r="155" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="155" spans="1:11" ht="18" customHeight="1">
       <c r="A155" s="6"/>
       <c r="B155" s="2" t="s">
         <v>268</v>
@@ -6757,7 +6771,7 @@
       <c r="J155" s="6"/>
       <c r="K155" s="6"/>
     </row>
-    <row r="156" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="156" spans="1:11" ht="18" customHeight="1">
       <c r="A156" s="6"/>
       <c r="B156" s="2" t="s">
         <v>269</v>
@@ -6776,7 +6790,7 @@
       <c r="J156" s="6"/>
       <c r="K156" s="6"/>
     </row>
-    <row r="157" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="157" spans="1:11" ht="18" customHeight="1">
       <c r="A157" s="6"/>
       <c r="B157" s="2" t="s">
         <v>270</v>
@@ -6795,7 +6809,7 @@
       <c r="J157" s="6"/>
       <c r="K157" s="6"/>
     </row>
-    <row r="158" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="158" spans="1:11" ht="18" customHeight="1">
       <c r="A158" s="6"/>
       <c r="B158" s="2" t="s">
         <v>272</v>
@@ -6814,7 +6828,7 @@
       <c r="J158" s="6"/>
       <c r="K158" s="6"/>
     </row>
-    <row r="159" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="159" spans="1:11" ht="18" customHeight="1">
       <c r="A159" s="6"/>
       <c r="B159" s="2" t="s">
         <v>274</v>
@@ -6833,7 +6847,7 @@
       <c r="J159" s="6"/>
       <c r="K159" s="6"/>
     </row>
-    <row r="160" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="160" spans="1:11" ht="18" customHeight="1">
       <c r="A160" s="6"/>
       <c r="B160" s="2" t="s">
         <v>276</v>
@@ -6852,7 +6866,7 @@
       <c r="J160" s="6"/>
       <c r="K160" s="6"/>
     </row>
-    <row r="161" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="161" spans="1:11" ht="18" customHeight="1">
       <c r="A161" s="6"/>
       <c r="B161" s="2" t="s">
         <v>278</v>
@@ -6871,7 +6885,7 @@
       <c r="J161" s="6"/>
       <c r="K161" s="6"/>
     </row>
-    <row r="162" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="162" spans="1:11" ht="18" customHeight="1">
       <c r="A162" s="6"/>
       <c r="B162" s="2" t="s">
         <v>280</v>
@@ -6890,7 +6904,7 @@
       <c r="J162" s="6"/>
       <c r="K162" s="6"/>
     </row>
-    <row r="163" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="163" spans="1:11" ht="18" customHeight="1">
       <c r="A163" s="6"/>
       <c r="B163" s="2" t="s">
         <v>282</v>
@@ -6909,7 +6923,7 @@
       <c r="J163" s="6"/>
       <c r="K163" s="6"/>
     </row>
-    <row r="164" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="164" spans="1:11" ht="18" customHeight="1">
       <c r="A164" s="6"/>
       <c r="B164" s="2" t="s">
         <v>284</v>
@@ -6928,7 +6942,7 @@
       <c r="J164" s="6"/>
       <c r="K164" s="6"/>
     </row>
-    <row r="165" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="165" spans="1:11" ht="18" customHeight="1">
       <c r="A165" s="6"/>
       <c r="B165" s="2" t="s">
         <v>286</v>
@@ -6947,7 +6961,7 @@
       <c r="J165" s="6"/>
       <c r="K165" s="6"/>
     </row>
-    <row r="166" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="166" spans="1:11" ht="18" customHeight="1">
       <c r="A166" s="6"/>
       <c r="B166" s="2" t="s">
         <v>288</v>
@@ -6968,7 +6982,7 @@
       <c r="J166" s="6"/>
       <c r="K166" s="6"/>
     </row>
-    <row r="167" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="167" spans="1:11" ht="18" customHeight="1">
       <c r="A167" s="6"/>
       <c r="B167" s="2" t="s">
         <v>291</v>
@@ -6989,7 +7003,7 @@
       <c r="J167" s="6"/>
       <c r="K167" s="6"/>
     </row>
-    <row r="168" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="168" spans="1:11" ht="18" customHeight="1">
       <c r="A168" s="6"/>
       <c r="B168" s="2" t="s">
         <v>293</v>
@@ -7008,7 +7022,7 @@
       <c r="J168" s="6"/>
       <c r="K168" s="6"/>
     </row>
-    <row r="169" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="169" spans="1:11" ht="18" customHeight="1">
       <c r="A169" s="6"/>
       <c r="B169" s="2" t="s">
         <v>295</v>
@@ -7027,7 +7041,7 @@
       <c r="J169" s="6"/>
       <c r="K169" s="6"/>
     </row>
-    <row r="170" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="170" spans="1:11" ht="18" customHeight="1">
       <c r="A170" s="6"/>
       <c r="B170" s="2" t="s">
         <v>297</v>
@@ -7046,7 +7060,7 @@
       <c r="J170" s="6"/>
       <c r="K170" s="6"/>
     </row>
-    <row r="171" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="171" spans="1:11" ht="18" customHeight="1">
       <c r="A171" s="6"/>
       <c r="B171" s="2" t="s">
         <v>298</v>
@@ -7065,7 +7079,7 @@
       <c r="J171" s="6"/>
       <c r="K171" s="6"/>
     </row>
-    <row r="172" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="172" spans="1:11" ht="18" customHeight="1">
       <c r="A172" s="6"/>
       <c r="B172" s="2" t="s">
         <v>299</v>
@@ -7084,7 +7098,7 @@
       <c r="J172" s="6"/>
       <c r="K172" s="6"/>
     </row>
-    <row r="173" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="173" spans="1:11" ht="18" customHeight="1">
       <c r="A173" s="6"/>
       <c r="B173" s="2" t="s">
         <v>301</v>
@@ -7103,7 +7117,7 @@
       <c r="J173" s="6"/>
       <c r="K173" s="6"/>
     </row>
-    <row r="174" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="174" spans="1:11" ht="18" customHeight="1">
       <c r="A174" s="6"/>
       <c r="B174" s="2" t="s">
         <v>303</v>
@@ -7122,7 +7136,7 @@
       <c r="J174" s="6"/>
       <c r="K174" s="6"/>
     </row>
-    <row r="175" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="175" spans="1:11" ht="18" customHeight="1">
       <c r="A175" s="6"/>
       <c r="B175" s="2" t="s">
         <v>306</v>
@@ -7141,7 +7155,7 @@
       <c r="J175" s="6"/>
       <c r="K175" s="6"/>
     </row>
-    <row r="176" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="176" spans="1:11" ht="18" customHeight="1">
       <c r="A176" s="6"/>
       <c r="B176" s="2" t="s">
         <v>308</v>
@@ -7160,7 +7174,7 @@
       <c r="J176" s="6"/>
       <c r="K176" s="6"/>
     </row>
-    <row r="177" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="177" spans="1:11" ht="18" customHeight="1">
       <c r="A177" s="1"/>
       <c r="B177" s="2" t="s">
         <v>291</v>
@@ -7200,7 +7214,7 @@
       <c r="J178" s="6"/>
       <c r="K178" s="6"/>
     </row>
-    <row r="179" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="179" spans="1:11" ht="18" customHeight="1">
       <c r="A179" s="6"/>
       <c r="B179" s="2" t="s">
         <v>313</v>
@@ -7221,7 +7235,7 @@
       <c r="J179" s="6"/>
       <c r="K179" s="6"/>
     </row>
-    <row r="180" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="180" spans="1:11" ht="18" customHeight="1">
       <c r="A180" s="6"/>
       <c r="B180" s="2" t="s">
         <v>316</v>
@@ -7240,7 +7254,7 @@
       <c r="J180" s="6"/>
       <c r="K180" s="6"/>
     </row>
-    <row r="181" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="181" spans="1:11" ht="18" customHeight="1">
       <c r="A181" s="6"/>
       <c r="B181" s="2" t="s">
         <v>318</v>
@@ -7259,7 +7273,7 @@
       <c r="J181" s="6"/>
       <c r="K181" s="6"/>
     </row>
-    <row r="182" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="182" spans="1:11" ht="18" customHeight="1">
       <c r="A182" s="6"/>
       <c r="B182" s="2" t="s">
         <v>320</v>
@@ -7278,7 +7292,7 @@
       <c r="J182" s="6"/>
       <c r="K182" s="6"/>
     </row>
-    <row r="183" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="183" spans="1:11" ht="18" customHeight="1">
       <c r="A183" s="6"/>
       <c r="B183" s="2" t="s">
         <v>323</v>
@@ -7297,7 +7311,7 @@
       <c r="J183" s="6"/>
       <c r="K183" s="6"/>
     </row>
-    <row r="184" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="184" spans="1:11" ht="18" customHeight="1">
       <c r="A184" s="6"/>
       <c r="B184" s="2" t="s">
         <v>325</v>
@@ -7316,7 +7330,7 @@
       <c r="J184" s="6"/>
       <c r="K184" s="6"/>
     </row>
-    <row r="185" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="185" spans="1:11" ht="18" customHeight="1">
       <c r="A185" s="1"/>
       <c r="B185" s="2" t="s">
         <v>327</v>
@@ -7337,7 +7351,7 @@
       <c r="J185" s="6"/>
       <c r="K185" s="6"/>
     </row>
-    <row r="186" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="186" spans="1:11" ht="18" customHeight="1">
       <c r="A186" s="6"/>
       <c r="B186" s="2" t="s">
         <v>330</v>
@@ -7356,7 +7370,7 @@
       <c r="J186" s="6"/>
       <c r="K186" s="6"/>
     </row>
-    <row r="187" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="187" spans="1:11" ht="18" customHeight="1">
       <c r="A187" s="1"/>
       <c r="B187" s="2" t="s">
         <v>332</v>
@@ -7375,7 +7389,7 @@
       <c r="J187" s="6"/>
       <c r="K187" s="6"/>
     </row>
-    <row r="188" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="188" spans="1:11" ht="18" customHeight="1">
       <c r="A188" s="6"/>
       <c r="B188" s="2" t="s">
         <v>333</v>
@@ -7394,7 +7408,7 @@
       <c r="J188" s="6"/>
       <c r="K188" s="6"/>
     </row>
-    <row r="189" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="189" spans="1:11" ht="18" customHeight="1">
       <c r="A189" s="6"/>
       <c r="B189" s="2" t="s">
         <v>334</v>
@@ -7413,7 +7427,7 @@
       <c r="J189" s="6"/>
       <c r="K189" s="6"/>
     </row>
-    <row r="190" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="190" spans="1:11" ht="18" customHeight="1">
       <c r="A190" s="1"/>
       <c r="B190" s="2" t="s">
         <v>336</v>
@@ -7432,7 +7446,7 @@
       <c r="J190" s="6"/>
       <c r="K190" s="6"/>
     </row>
-    <row r="191" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="191" spans="1:11" ht="18" customHeight="1">
       <c r="A191" s="6"/>
       <c r="B191" s="2" t="s">
         <v>338</v>
@@ -7451,7 +7465,7 @@
       <c r="J191" s="6"/>
       <c r="K191" s="6"/>
     </row>
-    <row r="192" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="192" spans="1:11" ht="18" customHeight="1">
       <c r="A192" s="6"/>
       <c r="B192" s="2" t="s">
         <v>340</v>
@@ -7470,7 +7484,7 @@
       <c r="J192" s="6"/>
       <c r="K192" s="6"/>
     </row>
-    <row r="193" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="193" spans="1:11" ht="18" customHeight="1">
       <c r="A193" s="6"/>
       <c r="B193" s="2" t="s">
         <v>342</v>
@@ -7489,7 +7503,7 @@
       <c r="J193" s="6"/>
       <c r="K193" s="6"/>
     </row>
-    <row r="194" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="194" spans="1:11" ht="18" customHeight="1">
       <c r="A194" s="6"/>
       <c r="B194" s="2" t="s">
         <v>344</v>
@@ -7508,7 +7522,7 @@
       <c r="J194" s="6"/>
       <c r="K194" s="6"/>
     </row>
-    <row r="195" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="195" spans="1:11" ht="18" customHeight="1">
       <c r="A195" s="6"/>
       <c r="B195" s="2" t="s">
         <v>345</v>
@@ -7527,7 +7541,7 @@
       <c r="J195" s="6"/>
       <c r="K195" s="6"/>
     </row>
-    <row r="196" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="196" spans="1:11" ht="18" customHeight="1">
       <c r="A196" s="6"/>
       <c r="B196" s="2" t="s">
         <v>346</v>
@@ -7546,7 +7560,7 @@
       <c r="J196" s="6"/>
       <c r="K196" s="6"/>
     </row>
-    <row r="197" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="197" spans="1:11" ht="18" customHeight="1">
       <c r="A197" s="6"/>
       <c r="B197" s="2" t="s">
         <v>348</v>
@@ -7565,7 +7579,7 @@
       <c r="J197" s="6"/>
       <c r="K197" s="6"/>
     </row>
-    <row r="198" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="198" spans="1:11" ht="18" customHeight="1">
       <c r="A198" s="6"/>
       <c r="B198" s="2" t="s">
         <v>350</v>
@@ -7586,7 +7600,7 @@
       <c r="J198" s="6"/>
       <c r="K198" s="6"/>
     </row>
-    <row r="199" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="199" spans="1:11" ht="18" customHeight="1">
       <c r="A199" s="6"/>
       <c r="B199" s="2" t="s">
         <v>353</v>
@@ -7605,7 +7619,7 @@
       <c r="J199" s="6"/>
       <c r="K199" s="6"/>
     </row>
-    <row r="200" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="200" spans="1:11" ht="18" customHeight="1">
       <c r="A200" s="6"/>
       <c r="B200" s="2" t="s">
         <v>355</v>
@@ -7624,7 +7638,7 @@
       <c r="J200" s="6"/>
       <c r="K200" s="6"/>
     </row>
-    <row r="201" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="201" spans="1:11" ht="18" customHeight="1">
       <c r="A201" s="6"/>
       <c r="B201" s="2" t="s">
         <v>356</v>
@@ -7643,7 +7657,7 @@
       <c r="J201" s="6"/>
       <c r="K201" s="6"/>
     </row>
-    <row r="202" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="202" spans="1:11" ht="18" customHeight="1">
       <c r="A202" s="6"/>
       <c r="B202" s="2" t="s">
         <v>358</v>
@@ -7664,7 +7678,7 @@
       <c r="J202" s="6"/>
       <c r="K202" s="6"/>
     </row>
-    <row r="203" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="203" spans="1:11" ht="18" customHeight="1">
       <c r="A203" s="1"/>
       <c r="B203" s="2" t="s">
         <v>361</v>
@@ -7683,7 +7697,7 @@
       <c r="J203" s="6"/>
       <c r="K203" s="6"/>
     </row>
-    <row r="204" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="204" spans="1:11" ht="18" customHeight="1">
       <c r="A204" s="6"/>
       <c r="B204" s="2" t="s">
         <v>362</v>
@@ -7702,7 +7716,7 @@
       <c r="J204" s="6"/>
       <c r="K204" s="6"/>
     </row>
-    <row r="205" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="205" spans="1:11" ht="18" customHeight="1">
       <c r="A205" s="6"/>
       <c r="B205" s="2" t="s">
         <v>363</v>
@@ -7721,7 +7735,7 @@
       <c r="J205" s="6"/>
       <c r="K205" s="6"/>
     </row>
-    <row r="206" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="206" spans="1:11" ht="18" customHeight="1">
       <c r="A206" s="6"/>
       <c r="B206" s="2" t="s">
         <v>364</v>
@@ -7740,7 +7754,7 @@
       <c r="J206" s="6"/>
       <c r="K206" s="6"/>
     </row>
-    <row r="207" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="207" spans="1:11" ht="18" customHeight="1">
       <c r="A207" s="6"/>
       <c r="B207" s="2" t="s">
         <v>365</v>
@@ -7759,7 +7773,7 @@
       <c r="J207" s="6"/>
       <c r="K207" s="6"/>
     </row>
-    <row r="208" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="208" spans="1:11" ht="18" customHeight="1">
       <c r="A208" s="6"/>
       <c r="B208" s="2" t="s">
         <v>366</v>
@@ -7778,7 +7792,7 @@
       <c r="J208" s="6"/>
       <c r="K208" s="6"/>
     </row>
-    <row r="209" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="209" spans="1:11" ht="18" customHeight="1">
       <c r="A209" s="6"/>
       <c r="B209" s="2" t="s">
         <v>367</v>
@@ -7797,7 +7811,7 @@
       <c r="J209" s="6"/>
       <c r="K209" s="6"/>
     </row>
-    <row r="210" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="210" spans="1:11" ht="18" customHeight="1">
       <c r="A210" s="6"/>
       <c r="B210" s="2" t="s">
         <v>368</v>
@@ -7816,7 +7830,7 @@
       <c r="J210" s="6"/>
       <c r="K210" s="6"/>
     </row>
-    <row r="211" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="211" spans="1:11" ht="18" customHeight="1">
       <c r="A211" s="1"/>
       <c r="B211" s="2" t="s">
         <v>369</v>
@@ -7835,7 +7849,7 @@
       <c r="J211" s="6"/>
       <c r="K211" s="6"/>
     </row>
-    <row r="212" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="212" spans="1:11" ht="18" customHeight="1">
       <c r="A212" s="6"/>
       <c r="B212" s="2" t="s">
         <v>370</v>
@@ -7854,7 +7868,7 @@
       <c r="J212" s="6"/>
       <c r="K212" s="6"/>
     </row>
-    <row r="213" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="213" spans="1:11" ht="18" customHeight="1">
       <c r="A213" s="6"/>
       <c r="B213" s="2" t="s">
         <v>371</v>
@@ -7873,7 +7887,7 @@
       <c r="J213" s="6"/>
       <c r="K213" s="6"/>
     </row>
-    <row r="214" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="214" spans="1:11" ht="18" customHeight="1">
       <c r="A214" s="1"/>
       <c r="B214" s="2" t="s">
         <v>372</v>
@@ -7892,7 +7906,7 @@
       <c r="J214" s="6"/>
       <c r="K214" s="6"/>
     </row>
-    <row r="215" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="215" spans="1:11" ht="18" customHeight="1">
       <c r="A215" s="6"/>
       <c r="B215" s="2" t="s">
         <v>373</v>
@@ -7911,7 +7925,7 @@
       <c r="J215" s="6"/>
       <c r="K215" s="6"/>
     </row>
-    <row r="216" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="216" spans="1:11" ht="18" customHeight="1">
       <c r="A216" s="6"/>
       <c r="B216" s="2" t="s">
         <v>374</v>
@@ -7930,7 +7944,7 @@
       <c r="J216" s="6"/>
       <c r="K216" s="6"/>
     </row>
-    <row r="217" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="217" spans="1:11" ht="18" customHeight="1">
       <c r="A217" s="6"/>
       <c r="B217" s="2" t="s">
         <v>375</v>
@@ -7949,7 +7963,7 @@
       <c r="J217" s="6"/>
       <c r="K217" s="6"/>
     </row>
-    <row r="218" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="218" spans="1:11" ht="18" customHeight="1">
       <c r="A218" s="6"/>
       <c r="B218" s="2" t="s">
         <v>376</v>
@@ -7968,7 +7982,7 @@
       <c r="J218" s="6"/>
       <c r="K218" s="6"/>
     </row>
-    <row r="219" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="219" spans="1:11" ht="18" customHeight="1">
       <c r="A219" s="6"/>
       <c r="B219" s="2" t="s">
         <v>378</v>
@@ -7987,7 +8001,7 @@
       <c r="J219" s="6"/>
       <c r="K219" s="6"/>
     </row>
-    <row r="220" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="220" spans="1:11" ht="18" customHeight="1">
       <c r="A220" s="6"/>
       <c r="B220" s="2" t="s">
         <v>380</v>
@@ -8006,7 +8020,7 @@
       <c r="J220" s="6"/>
       <c r="K220" s="6"/>
     </row>
-    <row r="221" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="221" spans="1:11" ht="18" customHeight="1">
       <c r="A221" s="1"/>
       <c r="B221" s="2" t="s">
         <v>381</v>
@@ -8025,7 +8039,7 @@
       <c r="J221" s="6"/>
       <c r="K221" s="6"/>
     </row>
-    <row r="222" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="222" spans="1:11" ht="18" customHeight="1">
       <c r="A222" s="6"/>
       <c r="B222" s="2" t="s">
         <v>382</v>
@@ -8044,7 +8058,7 @@
       <c r="J222" s="6"/>
       <c r="K222" s="6"/>
     </row>
-    <row r="223" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="223" spans="1:11" ht="18" customHeight="1">
       <c r="A223" s="6"/>
       <c r="B223" s="2" t="s">
         <v>384</v>
@@ -8063,7 +8077,7 @@
       <c r="J223" s="6"/>
       <c r="K223" s="6"/>
     </row>
-    <row r="224" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="224" spans="1:11" ht="18" customHeight="1">
       <c r="A224" s="6"/>
       <c r="B224" s="2" t="s">
         <v>386</v>
@@ -8082,7 +8096,7 @@
       <c r="J224" s="6"/>
       <c r="K224" s="6"/>
     </row>
-    <row r="225" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="225" spans="1:11" ht="18" customHeight="1">
       <c r="A225" s="1"/>
       <c r="B225" s="2" t="s">
         <v>388</v>
@@ -8101,7 +8115,7 @@
       <c r="J225" s="6"/>
       <c r="K225" s="6"/>
     </row>
-    <row r="226" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="226" spans="1:11" ht="18" customHeight="1">
       <c r="A226" s="6"/>
       <c r="B226" s="2" t="s">
         <v>390</v>
@@ -8122,7 +8136,7 @@
       <c r="J226" s="6"/>
       <c r="K226" s="6"/>
     </row>
-    <row r="227" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="227" spans="1:11" ht="18" customHeight="1">
       <c r="A227" s="6"/>
       <c r="B227" s="2" t="s">
         <v>392</v>
@@ -8143,7 +8157,7 @@
       <c r="J227" s="6"/>
       <c r="K227" s="6"/>
     </row>
-    <row r="228" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="228" spans="1:11" ht="18" customHeight="1">
       <c r="A228" s="6"/>
       <c r="B228" s="2" t="s">
         <v>393</v>
@@ -8162,7 +8176,7 @@
       <c r="J228" s="6"/>
       <c r="K228" s="6"/>
     </row>
-    <row r="229" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="229" spans="1:11" ht="18" customHeight="1">
       <c r="A229" s="6"/>
       <c r="B229" s="2" t="s">
         <v>394</v>
@@ -8181,7 +8195,7 @@
       <c r="J229" s="6"/>
       <c r="K229" s="6"/>
     </row>
-    <row r="230" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="230" spans="1:11" ht="18" customHeight="1">
       <c r="A230" s="1"/>
       <c r="B230" s="2" t="s">
         <v>395</v>
@@ -8200,7 +8214,7 @@
       <c r="J230" s="6"/>
       <c r="K230" s="6"/>
     </row>
-    <row r="231" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="231" spans="1:11" ht="18" customHeight="1">
       <c r="A231" s="6"/>
       <c r="B231" s="16" t="s">
         <v>396</v>
@@ -8221,7 +8235,7 @@
       <c r="J231" s="6"/>
       <c r="K231" s="6"/>
     </row>
-    <row r="232" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="232" spans="1:11" ht="18" customHeight="1">
       <c r="A232" s="6"/>
       <c r="B232" s="2" t="s">
         <v>398</v>
@@ -8242,7 +8256,7 @@
       <c r="J232" s="6"/>
       <c r="K232" s="6"/>
     </row>
-    <row r="233" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="233" spans="1:11" ht="18" customHeight="1">
       <c r="A233" s="1"/>
       <c r="B233" s="2" t="s">
         <v>399</v>
@@ -8261,7 +8275,7 @@
       <c r="J233" s="6"/>
       <c r="K233" s="6"/>
     </row>
-    <row r="234" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="234" spans="1:11" ht="18" customHeight="1">
       <c r="A234" s="1"/>
       <c r="B234" s="2" t="s">
         <v>400</v>
@@ -8280,7 +8294,7 @@
       <c r="J234" s="6"/>
       <c r="K234" s="6"/>
     </row>
-    <row r="235" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="235" spans="1:11" ht="18" customHeight="1">
       <c r="A235" s="6"/>
       <c r="B235" s="2" t="s">
         <v>401</v>
@@ -8301,7 +8315,7 @@
       <c r="J235" s="6"/>
       <c r="K235" s="6"/>
     </row>
-    <row r="236" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="236" spans="1:11" ht="18" customHeight="1">
       <c r="A236" s="6"/>
       <c r="B236" s="2" t="s">
         <v>403</v>
@@ -8320,7 +8334,7 @@
       <c r="J236" s="6"/>
       <c r="K236" s="6"/>
     </row>
-    <row r="237" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="237" spans="1:11" ht="18" customHeight="1">
       <c r="A237" s="6"/>
       <c r="B237" s="2" t="s">
         <v>404</v>
@@ -8341,7 +8355,7 @@
       <c r="J237" s="6"/>
       <c r="K237" s="6"/>
     </row>
-    <row r="238" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="238" spans="1:11" ht="18" customHeight="1">
       <c r="A238" s="6"/>
       <c r="B238" s="2" t="s">
         <v>406</v>
@@ -8362,7 +8376,7 @@
       <c r="J238" s="6"/>
       <c r="K238" s="6"/>
     </row>
-    <row r="239" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="239" spans="1:11" ht="18" customHeight="1">
       <c r="A239" s="6"/>
       <c r="B239" s="2" t="s">
         <v>408</v>
@@ -8383,7 +8397,7 @@
       <c r="J239" s="6"/>
       <c r="K239" s="6"/>
     </row>
-    <row r="240" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="240" spans="1:11" ht="18" customHeight="1">
       <c r="A240" s="6"/>
       <c r="B240" s="2" t="s">
         <v>410</v>
@@ -8406,7 +8420,7 @@
       <c r="J240" s="6"/>
       <c r="K240" s="6"/>
     </row>
-    <row r="241" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="241" spans="1:11" ht="18" customHeight="1">
       <c r="A241" s="6"/>
       <c r="B241" s="2" t="s">
         <v>412</v>
@@ -8425,7 +8439,7 @@
       <c r="J241" s="6"/>
       <c r="K241" s="6"/>
     </row>
-    <row r="242" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="242" spans="1:11" ht="18" customHeight="1">
       <c r="A242" s="6"/>
       <c r="B242" s="2" t="s">
         <v>414</v>
@@ -8444,7 +8458,7 @@
       <c r="J242" s="6"/>
       <c r="K242" s="6"/>
     </row>
-    <row r="243" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="243" spans="1:11" ht="18" customHeight="1">
       <c r="A243" s="6"/>
       <c r="B243" s="2" t="s">
         <v>416</v>
@@ -8463,7 +8477,7 @@
       <c r="J243" s="6"/>
       <c r="K243" s="6"/>
     </row>
-    <row r="244" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="244" spans="1:11" ht="18" customHeight="1">
       <c r="A244" s="6"/>
       <c r="B244" s="2" t="s">
         <v>418</v>
@@ -8484,7 +8498,7 @@
       <c r="J244" s="6"/>
       <c r="K244" s="6"/>
     </row>
-    <row r="245" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="245" spans="1:11" ht="18" customHeight="1">
       <c r="A245" s="6"/>
       <c r="B245" s="2" t="s">
         <v>421</v>
@@ -8503,7 +8517,7 @@
       <c r="J245" s="6"/>
       <c r="K245" s="6"/>
     </row>
-    <row r="246" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="246" spans="1:11" ht="18" customHeight="1">
       <c r="A246" s="6"/>
       <c r="B246" s="2" t="s">
         <v>423</v>
@@ -8522,7 +8536,7 @@
       <c r="J246" s="6"/>
       <c r="K246" s="6"/>
     </row>
-    <row r="247" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="247" spans="1:11" ht="18" customHeight="1">
       <c r="A247" s="6"/>
       <c r="B247" s="2" t="s">
         <v>425</v>
@@ -8541,7 +8555,7 @@
       <c r="J247" s="6"/>
       <c r="K247" s="6"/>
     </row>
-    <row r="248" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="248" spans="1:11" ht="18" customHeight="1">
       <c r="A248" s="1"/>
       <c r="B248" s="2" t="s">
         <v>427</v>
@@ -8560,7 +8574,7 @@
       <c r="J248" s="6"/>
       <c r="K248" s="6"/>
     </row>
-    <row r="249" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="249" spans="1:11" ht="18" customHeight="1">
       <c r="A249" s="6"/>
       <c r="B249" s="2" t="s">
         <v>429</v>
@@ -8579,7 +8593,7 @@
       <c r="J249" s="6"/>
       <c r="K249" s="6"/>
     </row>
-    <row r="250" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="250" spans="1:11" ht="18" customHeight="1">
       <c r="A250" s="1"/>
       <c r="B250" s="2" t="s">
         <v>431</v>
@@ -8598,7 +8612,7 @@
       <c r="J250" s="6"/>
       <c r="K250" s="6"/>
     </row>
-    <row r="251" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="251" spans="1:11" ht="18" customHeight="1">
       <c r="A251" s="1"/>
       <c r="B251" s="2" t="s">
         <v>432</v>
@@ -8617,7 +8631,7 @@
       <c r="J251" s="6"/>
       <c r="K251" s="6"/>
     </row>
-    <row r="252" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="252" spans="1:11" ht="18" customHeight="1">
       <c r="A252" s="6"/>
       <c r="B252" s="2" t="s">
         <v>433</v>
@@ -8638,7 +8652,7 @@
       <c r="J252" s="6"/>
       <c r="K252" s="6"/>
     </row>
-    <row r="253" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="253" spans="1:11" ht="18" customHeight="1">
       <c r="A253" s="6"/>
       <c r="B253" s="2" t="s">
         <v>434</v>
@@ -8657,7 +8671,7 @@
       <c r="J253" s="6"/>
       <c r="K253" s="6"/>
     </row>
-    <row r="254" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="254" spans="1:11" ht="18" customHeight="1">
       <c r="A254" s="6"/>
       <c r="B254" s="2" t="s">
         <v>435</v>
@@ -8676,7 +8690,7 @@
       <c r="J254" s="6"/>
       <c r="K254" s="6"/>
     </row>
-    <row r="255" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="255" spans="1:11" ht="18" customHeight="1">
       <c r="A255" s="6"/>
       <c r="B255" s="2" t="s">
         <v>436</v>
@@ -8695,7 +8709,7 @@
       <c r="J255" s="6"/>
       <c r="K255" s="6"/>
     </row>
-    <row r="256" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="256" spans="1:11" ht="18" customHeight="1">
       <c r="A256" s="6"/>
       <c r="B256" s="2" t="s">
         <v>437</v>
@@ -8716,7 +8730,7 @@
       <c r="J256" s="6"/>
       <c r="K256" s="6"/>
     </row>
-    <row r="257" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="257" spans="1:11" ht="18" customHeight="1">
       <c r="A257" s="6"/>
       <c r="B257" s="2" t="s">
         <v>438</v>
@@ -8735,7 +8749,7 @@
       <c r="J257" s="6"/>
       <c r="K257" s="6"/>
     </row>
-    <row r="258" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="258" spans="1:11" ht="18" customHeight="1">
       <c r="A258" s="6"/>
       <c r="B258" s="2" t="s">
         <v>439</v>
@@ -8754,7 +8768,7 @@
       <c r="J258" s="6"/>
       <c r="K258" s="6"/>
     </row>
-    <row r="259" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="259" spans="1:11" ht="18" customHeight="1">
       <c r="A259" s="6"/>
       <c r="B259" s="2" t="s">
         <v>440</v>
@@ -8773,7 +8787,7 @@
       <c r="J259" s="6"/>
       <c r="K259" s="6"/>
     </row>
-    <row r="260" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="260" spans="1:11" ht="18" customHeight="1">
       <c r="A260" s="6"/>
       <c r="B260" s="2" t="s">
         <v>441</v>
@@ -8794,7 +8808,7 @@
       <c r="J260" s="6"/>
       <c r="K260" s="6"/>
     </row>
-    <row r="261" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="261" spans="1:11" ht="18" customHeight="1">
       <c r="A261" s="6"/>
       <c r="B261" s="2" t="s">
         <v>442</v>
@@ -8815,7 +8829,7 @@
       <c r="J261" s="6"/>
       <c r="K261" s="6"/>
     </row>
-    <row r="262" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="262" spans="1:11" ht="18" customHeight="1">
       <c r="A262" s="17">
         <v>200</v>
       </c>
@@ -8838,7 +8852,7 @@
       <c r="J262" s="6"/>
       <c r="K262" s="6"/>
     </row>
-    <row r="263" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="263" spans="1:11" ht="18" customHeight="1">
       <c r="A263" s="6"/>
       <c r="B263" s="2" t="s">
         <v>444</v>
@@ -8857,7 +8871,7 @@
       <c r="J263" s="6"/>
       <c r="K263" s="6"/>
     </row>
-    <row r="264" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="264" spans="1:11" ht="18" customHeight="1">
       <c r="A264" s="6"/>
       <c r="B264" s="2" t="s">
         <v>445</v>
@@ -8878,7 +8892,7 @@
       <c r="J264" s="6"/>
       <c r="K264" s="6"/>
     </row>
-    <row r="265" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="265" spans="1:11" ht="18" customHeight="1">
       <c r="A265" s="6"/>
       <c r="B265" s="2" t="s">
         <v>447</v>
@@ -8897,7 +8911,7 @@
       <c r="J265" s="6"/>
       <c r="K265" s="6"/>
     </row>
-    <row r="266" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="266" spans="1:11" ht="18" customHeight="1">
       <c r="A266" s="6"/>
       <c r="B266" s="2" t="s">
         <v>448</v>
@@ -8918,7 +8932,7 @@
       <c r="J266" s="6"/>
       <c r="K266" s="6"/>
     </row>
-    <row r="267" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="267" spans="1:11" ht="18" customHeight="1">
       <c r="A267" s="6"/>
       <c r="B267" s="2" t="s">
         <v>449</v>
@@ -8937,7 +8951,7 @@
       <c r="J267" s="6"/>
       <c r="K267" s="6"/>
     </row>
-    <row r="268" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="268" spans="1:11" ht="18" customHeight="1">
       <c r="A268" s="6"/>
       <c r="B268" s="12" t="s">
         <v>450</v>
@@ -8958,7 +8972,7 @@
       <c r="J268" s="6"/>
       <c r="K268" s="6"/>
     </row>
-    <row r="269" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="269" spans="1:11" ht="18" customHeight="1">
       <c r="A269" s="6"/>
       <c r="B269" s="12" t="s">
         <v>452</v>
@@ -8977,7 +8991,7 @@
       <c r="J269" s="6"/>
       <c r="K269" s="6"/>
     </row>
-    <row r="270" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="270" spans="1:11" ht="18" customHeight="1">
       <c r="A270" s="6"/>
       <c r="B270" s="12" t="s">
         <v>453</v>
@@ -8998,7 +9012,7 @@
       <c r="J270" s="6"/>
       <c r="K270" s="6"/>
     </row>
-    <row r="271" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="271" spans="1:11" ht="18" customHeight="1">
       <c r="A271" s="6"/>
       <c r="B271" s="2" t="s">
         <v>455</v>
@@ -9017,7 +9031,7 @@
       <c r="J271" s="6"/>
       <c r="K271" s="6"/>
     </row>
-    <row r="272" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="272" spans="1:11" ht="18" customHeight="1">
       <c r="A272" s="6"/>
       <c r="B272" s="2" t="s">
         <v>457</v>
@@ -9036,7 +9050,7 @@
       <c r="J272" s="6"/>
       <c r="K272" s="6"/>
     </row>
-    <row r="273" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="273" spans="1:11" ht="18" customHeight="1">
       <c r="A273" s="6"/>
       <c r="B273" s="2" t="s">
         <v>458</v>
@@ -9055,7 +9069,7 @@
       <c r="J273" s="6"/>
       <c r="K273" s="6"/>
     </row>
-    <row r="274" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="274" spans="1:11" ht="18" customHeight="1">
       <c r="A274" s="6"/>
       <c r="B274" s="2" t="s">
         <v>459</v>
@@ -9076,7 +9090,7 @@
       <c r="J274" s="6"/>
       <c r="K274" s="6"/>
     </row>
-    <row r="275" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="275" spans="1:11" ht="18" customHeight="1">
       <c r="A275" s="6"/>
       <c r="B275" s="2" t="s">
         <v>461</v>
@@ -9095,7 +9109,7 @@
       <c r="J275" s="6"/>
       <c r="K275" s="6"/>
     </row>
-    <row r="276" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="276" spans="1:11" ht="18" customHeight="1">
       <c r="A276" s="6"/>
       <c r="B276" s="2" t="s">
         <v>463</v>
@@ -9114,7 +9128,7 @@
       <c r="J276" s="6"/>
       <c r="K276" s="6"/>
     </row>
-    <row r="277" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="277" spans="1:11" ht="18" customHeight="1">
       <c r="A277" s="6"/>
       <c r="B277" s="2" t="s">
         <v>465</v>
@@ -9133,7 +9147,7 @@
       <c r="J277" s="6"/>
       <c r="K277" s="6"/>
     </row>
-    <row r="278" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="278" spans="1:11" ht="18" customHeight="1">
       <c r="A278" s="6"/>
       <c r="B278" s="2" t="s">
         <v>467</v>
@@ -9154,7 +9168,7 @@
       <c r="J278" s="6"/>
       <c r="K278" s="6"/>
     </row>
-    <row r="279" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="279" spans="1:11" ht="18" customHeight="1">
       <c r="A279" s="6"/>
       <c r="B279" s="2" t="s">
         <v>468</v>
@@ -9173,7 +9187,7 @@
       <c r="J279" s="6"/>
       <c r="K279" s="6"/>
     </row>
-    <row r="280" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="280" spans="1:11" ht="18" customHeight="1">
       <c r="A280" s="6"/>
       <c r="B280" s="2" t="s">
         <v>470</v>
@@ -9194,7 +9208,7 @@
       <c r="J280" s="6"/>
       <c r="K280" s="6"/>
     </row>
-    <row r="281" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="281" spans="1:11" ht="18" customHeight="1">
       <c r="A281" s="6"/>
       <c r="B281" s="2" t="s">
         <v>472</v>
@@ -9213,7 +9227,7 @@
       <c r="J281" s="6"/>
       <c r="K281" s="6"/>
     </row>
-    <row r="282" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="282" spans="1:11" ht="18" customHeight="1">
       <c r="A282" s="6"/>
       <c r="B282" s="2" t="s">
         <v>474</v>
@@ -9232,7 +9246,7 @@
       <c r="J282" s="6"/>
       <c r="K282" s="6"/>
     </row>
-    <row r="283" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="283" spans="1:11" ht="18" customHeight="1">
       <c r="A283" s="6"/>
       <c r="B283" s="2" t="s">
         <v>476</v>
@@ -9253,7 +9267,7 @@
       <c r="J283" s="6"/>
       <c r="K283" s="6"/>
     </row>
-    <row r="284" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="284" spans="1:11" ht="18" customHeight="1">
       <c r="A284" s="6"/>
       <c r="B284" s="2" t="s">
         <v>479</v>
@@ -9276,7 +9290,7 @@
       <c r="J284" s="6"/>
       <c r="K284" s="6"/>
     </row>
-    <row r="285" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="285" spans="1:11" ht="18" customHeight="1">
       <c r="A285" s="6"/>
       <c r="B285" s="2" t="s">
         <v>482</v>
@@ -9295,7 +9309,7 @@
       <c r="J285" s="6"/>
       <c r="K285" s="6"/>
     </row>
-    <row r="286" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="286" spans="1:11" ht="18" customHeight="1">
       <c r="A286" s="6"/>
       <c r="B286" s="2" t="s">
         <v>484</v>
@@ -9314,7 +9328,7 @@
       <c r="J286" s="6"/>
       <c r="K286" s="6"/>
     </row>
-    <row r="287" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="287" spans="1:11" ht="18" customHeight="1">
       <c r="A287" s="6"/>
       <c r="B287" s="2" t="s">
         <v>485</v>
@@ -9333,7 +9347,7 @@
       <c r="J287" s="6"/>
       <c r="K287" s="6"/>
     </row>
-    <row r="288" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="288" spans="1:11" ht="18" customHeight="1">
       <c r="A288" s="6"/>
       <c r="B288" s="2" t="s">
         <v>486</v>
@@ -9354,7 +9368,7 @@
       <c r="J288" s="6"/>
       <c r="K288" s="6"/>
     </row>
-    <row r="289" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="289" spans="1:11" ht="18" customHeight="1">
       <c r="A289" s="1"/>
       <c r="B289" s="2" t="s">
         <v>488</v>
@@ -9373,7 +9387,7 @@
       <c r="J289" s="6"/>
       <c r="K289" s="6"/>
     </row>
-    <row r="290" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="290" spans="1:11" ht="18" customHeight="1">
       <c r="A290" s="1"/>
       <c r="B290" s="2" t="s">
         <v>489</v>
@@ -9392,7 +9406,7 @@
       <c r="J290" s="6"/>
       <c r="K290" s="6"/>
     </row>
-    <row r="291" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="291" spans="1:11" ht="18" customHeight="1">
       <c r="A291" s="1"/>
       <c r="B291" s="2" t="s">
         <v>490</v>
@@ -9411,7 +9425,7 @@
       <c r="J291" s="6"/>
       <c r="K291" s="6"/>
     </row>
-    <row r="292" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="292" spans="1:11" ht="18" customHeight="1">
       <c r="A292" s="6"/>
       <c r="B292" s="2" t="s">
         <v>491</v>
@@ -9430,7 +9444,7 @@
       <c r="J292" s="6"/>
       <c r="K292" s="6"/>
     </row>
-    <row r="293" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="293" spans="1:11" ht="18" customHeight="1">
       <c r="A293" s="6"/>
       <c r="B293" s="2" t="s">
         <v>493</v>
@@ -9449,7 +9463,7 @@
       <c r="J293" s="6"/>
       <c r="K293" s="6"/>
     </row>
-    <row r="294" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="294" spans="1:11" ht="18" customHeight="1">
       <c r="A294" s="6"/>
       <c r="B294" s="2" t="s">
         <v>495</v>
@@ -9468,7 +9482,7 @@
       <c r="J294" s="6"/>
       <c r="K294" s="6"/>
     </row>
-    <row r="295" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="295" spans="1:11" ht="18" customHeight="1">
       <c r="A295" s="6"/>
       <c r="B295" s="2" t="s">
         <v>497</v>
@@ -9487,7 +9501,7 @@
       <c r="J295" s="6"/>
       <c r="K295" s="6"/>
     </row>
-    <row r="296" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="296" spans="1:11" ht="18" customHeight="1">
       <c r="A296" s="6"/>
       <c r="B296" s="2" t="s">
         <v>499</v>
@@ -9506,7 +9520,7 @@
       <c r="J296" s="6"/>
       <c r="K296" s="6"/>
     </row>
-    <row r="297" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="297" spans="1:11" ht="18" customHeight="1">
       <c r="A297" s="6"/>
       <c r="B297" s="2" t="s">
         <v>500</v>
@@ -9525,7 +9539,7 @@
       <c r="J297" s="6"/>
       <c r="K297" s="6"/>
     </row>
-    <row r="298" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="298" spans="1:11" ht="18" customHeight="1">
       <c r="A298" s="6"/>
       <c r="B298" s="2" t="s">
         <v>501</v>
@@ -9544,7 +9558,7 @@
       <c r="J298" s="6"/>
       <c r="K298" s="6"/>
     </row>
-    <row r="299" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="299" spans="1:11" ht="18" customHeight="1">
       <c r="A299" s="6"/>
       <c r="B299" s="2" t="s">
         <v>502</v>
@@ -9563,7 +9577,7 @@
       <c r="J299" s="6"/>
       <c r="K299" s="6"/>
     </row>
-    <row r="300" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="300" spans="1:11" ht="18" customHeight="1">
       <c r="A300" s="6"/>
       <c r="B300" s="2" t="s">
         <v>503</v>
@@ -9586,7 +9600,7 @@
       <c r="J300" s="6"/>
       <c r="K300" s="6"/>
     </row>
-    <row r="301" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="301" spans="1:11" ht="18" customHeight="1">
       <c r="A301" s="6"/>
       <c r="B301" s="2" t="s">
         <v>506</v>
@@ -9605,7 +9619,7 @@
       <c r="J301" s="6"/>
       <c r="K301" s="6"/>
     </row>
-    <row r="302" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="302" spans="1:11" ht="18" customHeight="1">
       <c r="A302" s="1"/>
       <c r="B302" s="2" t="s">
         <v>508</v>
@@ -9624,7 +9638,7 @@
       <c r="J302" s="6"/>
       <c r="K302" s="6"/>
     </row>
-    <row r="303" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="303" spans="1:11" ht="18" customHeight="1">
       <c r="A303" s="17">
         <v>200</v>
       </c>
@@ -9649,7 +9663,7 @@
       <c r="J303" s="6"/>
       <c r="K303" s="6"/>
     </row>
-    <row r="304" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="304" spans="1:11" ht="18" customHeight="1">
       <c r="A304" s="6"/>
       <c r="B304" s="2" t="s">
         <v>513</v>
@@ -9668,7 +9682,7 @@
       <c r="J304" s="6"/>
       <c r="K304" s="6"/>
     </row>
-    <row r="305" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="305" spans="1:11" ht="18" customHeight="1">
       <c r="A305" s="1"/>
       <c r="B305" s="2" t="s">
         <v>515</v>
@@ -9687,7 +9701,7 @@
       <c r="J305" s="6"/>
       <c r="K305" s="6"/>
     </row>
-    <row r="306" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="306" spans="1:11" ht="18" customHeight="1">
       <c r="A306" s="6"/>
       <c r="B306" s="2" t="s">
         <v>518</v>
@@ -9706,7 +9720,7 @@
       <c r="J306" s="6"/>
       <c r="K306" s="6"/>
     </row>
-    <row r="307" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="307" spans="1:11" ht="18" customHeight="1">
       <c r="A307" s="6"/>
       <c r="B307" s="2" t="s">
         <v>520</v>
@@ -9727,7 +9741,7 @@
       <c r="J307" s="6"/>
       <c r="K307" s="6"/>
     </row>
-    <row r="308" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="308" spans="1:11" ht="18" customHeight="1">
       <c r="A308" s="6"/>
       <c r="B308" s="2" t="s">
         <v>523</v>
@@ -9746,7 +9760,7 @@
       <c r="J308" s="6"/>
       <c r="K308" s="6"/>
     </row>
-    <row r="309" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="309" spans="1:11" ht="18" customHeight="1">
       <c r="A309" s="6"/>
       <c r="B309" s="2" t="s">
         <v>525</v>
@@ -9765,7 +9779,7 @@
       <c r="J309" s="6"/>
       <c r="K309" s="6"/>
     </row>
-    <row r="310" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="310" spans="1:11" ht="18" customHeight="1">
       <c r="A310" s="6"/>
       <c r="B310" s="2" t="s">
         <v>527</v>
@@ -9784,7 +9798,7 @@
       <c r="J310" s="6"/>
       <c r="K310" s="6"/>
     </row>
-    <row r="311" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="311" spans="1:11" ht="18" customHeight="1">
       <c r="A311" s="6"/>
       <c r="B311" s="2" t="s">
         <v>528</v>
@@ -9807,7 +9821,7 @@
       <c r="J311" s="6"/>
       <c r="K311" s="6"/>
     </row>
-    <row r="312" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="312" spans="1:11" ht="18" customHeight="1">
       <c r="A312" s="6"/>
       <c r="B312" s="2" t="s">
         <v>531</v>
@@ -9826,7 +9840,7 @@
       <c r="J312" s="6"/>
       <c r="K312" s="6"/>
     </row>
-    <row r="313" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="313" spans="1:11" ht="18" customHeight="1">
       <c r="A313" s="6"/>
       <c r="B313" s="2" t="s">
         <v>533</v>
@@ -9845,7 +9859,7 @@
       <c r="J313" s="6"/>
       <c r="K313" s="6"/>
     </row>
-    <row r="314" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="314" spans="1:11" ht="18" customHeight="1">
       <c r="A314" s="6"/>
       <c r="B314" s="2" t="s">
         <v>535</v>
@@ -9866,7 +9880,7 @@
       <c r="J314" s="6"/>
       <c r="K314" s="6"/>
     </row>
-    <row r="315" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="315" spans="1:11" ht="18" customHeight="1">
       <c r="A315" s="6"/>
       <c r="B315" s="2" t="s">
         <v>537</v>
@@ -9885,7 +9899,7 @@
       <c r="J315" s="6"/>
       <c r="K315" s="6"/>
     </row>
-    <row r="316" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="316" spans="1:11" ht="18" customHeight="1">
       <c r="A316" s="6"/>
       <c r="B316" s="2" t="s">
         <v>539</v>
@@ -9904,7 +9918,7 @@
       <c r="J316" s="6"/>
       <c r="K316" s="6"/>
     </row>
-    <row r="317" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="317" spans="1:11" ht="18" customHeight="1">
       <c r="A317" s="6"/>
       <c r="B317" s="2" t="s">
         <v>541</v>
@@ -9923,7 +9937,7 @@
       <c r="J317" s="6"/>
       <c r="K317" s="6"/>
     </row>
-    <row r="318" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="318" spans="1:11" ht="18" customHeight="1">
       <c r="A318" s="6"/>
       <c r="B318" s="2" t="s">
         <v>542</v>
@@ -9942,7 +9956,7 @@
       <c r="J318" s="6"/>
       <c r="K318" s="6"/>
     </row>
-    <row r="319" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="319" spans="1:11" ht="18" customHeight="1">
       <c r="A319" s="6"/>
       <c r="B319" s="2" t="s">
         <v>544</v>
@@ -9961,7 +9975,7 @@
       <c r="J319" s="6"/>
       <c r="K319" s="6"/>
     </row>
-    <row r="320" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="320" spans="1:11" ht="18" customHeight="1">
       <c r="A320" s="6"/>
       <c r="B320" s="2" t="s">
         <v>546</v>
@@ -9980,7 +9994,7 @@
       <c r="J320" s="6"/>
       <c r="K320" s="6"/>
     </row>
-    <row r="321" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="321" spans="1:11" ht="18" customHeight="1">
       <c r="A321" s="6"/>
       <c r="B321" s="2" t="s">
         <v>547</v>
@@ -9999,7 +10013,7 @@
       <c r="J321" s="6"/>
       <c r="K321" s="6"/>
     </row>
-    <row r="322" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="322" spans="1:11" ht="18" customHeight="1">
       <c r="A322" s="6"/>
       <c r="B322" s="2" t="s">
         <v>548</v>
@@ -10020,7 +10034,7 @@
       <c r="J322" s="6"/>
       <c r="K322" s="6"/>
     </row>
-    <row r="323" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="323" spans="1:11" ht="18" customHeight="1">
       <c r="A323" s="6"/>
       <c r="B323" s="2" t="s">
         <v>549</v>
@@ -10039,7 +10053,7 @@
       <c r="J323" s="6"/>
       <c r="K323" s="6"/>
     </row>
-    <row r="324" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="324" spans="1:11" ht="18" customHeight="1">
       <c r="A324" s="6"/>
       <c r="B324" s="2" t="s">
         <v>550</v>
@@ -10058,7 +10072,7 @@
       <c r="J324" s="6"/>
       <c r="K324" s="6"/>
     </row>
-    <row r="325" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="325" spans="1:11" ht="18" customHeight="1">
       <c r="A325" s="6"/>
       <c r="B325" s="2" t="s">
         <v>551</v>
@@ -10077,7 +10091,7 @@
       <c r="J325" s="6"/>
       <c r="K325" s="6"/>
     </row>
-    <row r="326" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="326" spans="1:11" ht="18" customHeight="1">
       <c r="A326" s="6"/>
       <c r="B326" s="2" t="s">
         <v>553</v>
@@ -10096,7 +10110,7 @@
       <c r="J326" s="6"/>
       <c r="K326" s="6"/>
     </row>
-    <row r="327" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="327" spans="1:11" ht="18" customHeight="1">
       <c r="A327" s="6"/>
       <c r="B327" s="2" t="s">
         <v>554</v>
@@ -10115,7 +10129,7 @@
       <c r="J327" s="6"/>
       <c r="K327" s="6"/>
     </row>
-    <row r="328" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="328" spans="1:11" ht="18" customHeight="1">
       <c r="A328" s="1"/>
       <c r="B328" s="2" t="s">
         <v>555</v>
@@ -10134,7 +10148,7 @@
       <c r="J328" s="6"/>
       <c r="K328" s="6"/>
     </row>
-    <row r="329" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="329" spans="1:11" ht="18" customHeight="1">
       <c r="A329" s="1"/>
       <c r="B329" s="12" t="s">
         <v>557</v>
@@ -10153,7 +10167,7 @@
       <c r="J329" s="6"/>
       <c r="K329" s="6"/>
     </row>
-    <row r="330" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="330" spans="1:11" ht="18" customHeight="1">
       <c r="A330" s="6"/>
       <c r="B330" s="12" t="s">
         <v>559</v>
@@ -10172,7 +10186,7 @@
       <c r="J330" s="6"/>
       <c r="K330" s="6"/>
     </row>
-    <row r="331" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="331" spans="1:11" ht="18" customHeight="1">
       <c r="A331" s="6"/>
       <c r="B331" s="2" t="s">
         <v>560</v>
@@ -10191,7 +10205,7 @@
       <c r="J331" s="6"/>
       <c r="K331" s="6"/>
     </row>
-    <row r="332" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="332" spans="1:11" ht="18" customHeight="1">
       <c r="A332" s="6"/>
       <c r="B332" s="2" t="s">
         <v>561</v>
@@ -10210,7 +10224,7 @@
       <c r="J332" s="6"/>
       <c r="K332" s="6"/>
     </row>
-    <row r="333" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="333" spans="1:11" ht="18" customHeight="1">
       <c r="A333" s="6"/>
       <c r="B333" s="2" t="s">
         <v>562</v>
@@ -10229,7 +10243,7 @@
       <c r="J333" s="6"/>
       <c r="K333" s="6"/>
     </row>
-    <row r="334" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="334" spans="1:11" ht="18" customHeight="1">
       <c r="A334" s="6"/>
       <c r="B334" s="2" t="s">
         <v>564</v>
@@ -10248,7 +10262,7 @@
       <c r="J334" s="6"/>
       <c r="K334" s="6"/>
     </row>
-    <row r="335" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="335" spans="1:11" ht="18" customHeight="1">
       <c r="A335" s="6"/>
       <c r="B335" s="2" t="s">
         <v>565</v>
@@ -10267,7 +10281,7 @@
       <c r="J335" s="6"/>
       <c r="K335" s="6"/>
     </row>
-    <row r="336" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="336" spans="1:11" ht="18" customHeight="1">
       <c r="A336" s="6"/>
       <c r="B336" s="2" t="s">
         <v>568</v>
@@ -10286,7 +10300,7 @@
       <c r="J336" s="6"/>
       <c r="K336" s="6"/>
     </row>
-    <row r="337" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="337" spans="1:11" ht="18" customHeight="1">
       <c r="A337" s="6"/>
       <c r="B337" s="2" t="s">
         <v>570</v>
@@ -10305,7 +10319,7 @@
       <c r="J337" s="6"/>
       <c r="K337" s="6"/>
     </row>
-    <row r="338" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="338" spans="1:11" ht="18" customHeight="1">
       <c r="A338" s="6"/>
       <c r="B338" s="2" t="s">
         <v>571</v>
@@ -10324,7 +10338,7 @@
       <c r="J338" s="6"/>
       <c r="K338" s="6"/>
     </row>
-    <row r="339" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="339" spans="1:11" ht="18" customHeight="1">
       <c r="A339" s="6"/>
       <c r="B339" s="2" t="s">
         <v>572</v>
@@ -10343,7 +10357,7 @@
       <c r="J339" s="6"/>
       <c r="K339" s="6"/>
     </row>
-    <row r="340" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="340" spans="1:11" ht="18" customHeight="1">
       <c r="A340" s="1"/>
       <c r="B340" s="2" t="s">
         <v>573</v>
@@ -10362,7 +10376,7 @@
       <c r="J340" s="6"/>
       <c r="K340" s="6"/>
     </row>
-    <row r="341" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="341" spans="1:11" ht="18" customHeight="1">
       <c r="A341" s="6"/>
       <c r="B341" s="2" t="s">
         <v>575</v>
@@ -10381,7 +10395,7 @@
       <c r="J341" s="6"/>
       <c r="K341" s="6"/>
     </row>
-    <row r="342" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="342" spans="1:11" ht="18" customHeight="1">
       <c r="A342" s="6"/>
       <c r="B342" s="2" t="s">
         <v>577</v>
@@ -10402,7 +10416,7 @@
       <c r="J342" s="6"/>
       <c r="K342" s="6"/>
     </row>
-    <row r="343" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="343" spans="1:11" ht="18" customHeight="1">
       <c r="A343" s="1"/>
       <c r="B343" s="2" t="s">
         <v>580</v>
@@ -10421,7 +10435,7 @@
       <c r="J343" s="6"/>
       <c r="K343" s="6"/>
     </row>
-    <row r="344" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="344" spans="1:11" ht="18" customHeight="1">
       <c r="A344" s="6"/>
       <c r="B344" s="2" t="s">
         <v>581</v>
@@ -10440,7 +10454,7 @@
       <c r="J344" s="6"/>
       <c r="K344" s="6"/>
     </row>
-    <row r="345" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="345" spans="1:11" ht="18" customHeight="1">
       <c r="A345" s="1"/>
       <c r="B345" s="2" t="s">
         <v>582</v>
@@ -10459,7 +10473,7 @@
       <c r="J345" s="1"/>
       <c r="K345" s="1"/>
     </row>
-    <row r="346" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="346" spans="1:11" ht="18" customHeight="1">
       <c r="A346" s="1"/>
       <c r="B346" s="2" t="s">
         <v>583</v>
@@ -10478,7 +10492,7 @@
       <c r="J346" s="1"/>
       <c r="K346" s="1"/>
     </row>
-    <row r="347" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="347" spans="1:11" ht="18" customHeight="1">
       <c r="A347" s="6"/>
       <c r="B347" s="2" t="s">
         <v>584</v>
@@ -10497,7 +10511,7 @@
       <c r="J347" s="1"/>
       <c r="K347" s="1"/>
     </row>
-    <row r="348" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="348" spans="1:11" ht="18" customHeight="1">
       <c r="A348" s="6"/>
       <c r="B348" s="2" t="s">
         <v>585</v>
@@ -10516,7 +10530,7 @@
       <c r="J348" s="1"/>
       <c r="K348" s="1"/>
     </row>
-    <row r="349" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="349" spans="1:11" ht="18" customHeight="1">
       <c r="A349" s="1"/>
       <c r="B349" s="2" t="s">
         <v>586</v>
@@ -10535,7 +10549,7 @@
       <c r="J349" s="1"/>
       <c r="K349" s="1"/>
     </row>
-    <row r="350" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="350" spans="1:11" ht="18" customHeight="1">
       <c r="A350" s="1"/>
       <c r="B350" s="2" t="s">
         <v>587</v>
@@ -10554,7 +10568,7 @@
       <c r="J350" s="1"/>
       <c r="K350" s="1"/>
     </row>
-    <row r="351" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="351" spans="1:11" ht="18" customHeight="1">
       <c r="A351" s="6"/>
       <c r="B351" s="2" t="s">
         <v>588</v>
@@ -10573,7 +10587,7 @@
       <c r="J351" s="1"/>
       <c r="K351" s="1"/>
     </row>
-    <row r="352" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="352" spans="1:11" ht="18" customHeight="1">
       <c r="A352" s="1"/>
       <c r="B352" s="2" t="s">
         <v>589</v>
@@ -10592,7 +10606,7 @@
       <c r="J352" s="1"/>
       <c r="K352" s="1"/>
     </row>
-    <row r="353" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="353" spans="1:11" ht="18" customHeight="1">
       <c r="A353" s="1"/>
       <c r="B353" s="2" t="s">
         <v>590</v>
@@ -10611,7 +10625,7 @@
       <c r="J353" s="1"/>
       <c r="K353" s="1"/>
     </row>
-    <row r="354" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="354" spans="1:11" ht="18" customHeight="1">
       <c r="A354" s="1"/>
       <c r="B354" s="2" t="s">
         <v>591</v>
@@ -10630,7 +10644,7 @@
       <c r="J354" s="1"/>
       <c r="K354" s="1"/>
     </row>
-    <row r="355" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="355" spans="1:11" ht="18" customHeight="1">
       <c r="A355" s="1"/>
       <c r="B355" s="2" t="s">
         <v>291</v>
@@ -10649,7 +10663,7 @@
       <c r="J355" s="1"/>
       <c r="K355" s="1"/>
     </row>
-    <row r="356" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="356" spans="1:11" ht="18" customHeight="1">
       <c r="A356" s="1"/>
       <c r="B356" s="2" t="s">
         <v>592</v>
@@ -10668,7 +10682,7 @@
       <c r="J356" s="1"/>
       <c r="K356" s="1"/>
     </row>
-    <row r="357" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="357" spans="1:11" ht="18" customHeight="1">
       <c r="A357" s="6"/>
       <c r="B357" s="2" t="s">
         <v>593</v>
@@ -10689,7 +10703,7 @@
       <c r="J357" s="1"/>
       <c r="K357" s="1"/>
     </row>
-    <row r="358" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="358" spans="1:11" ht="18" customHeight="1">
       <c r="A358" s="6"/>
       <c r="B358" s="2" t="s">
         <v>596</v>
@@ -10708,7 +10722,7 @@
       <c r="J358" s="1"/>
       <c r="K358" s="1"/>
     </row>
-    <row r="359" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="359" spans="1:11" ht="18" customHeight="1">
       <c r="A359" s="6"/>
       <c r="B359" s="2" t="s">
         <v>598</v>
@@ -10727,7 +10741,7 @@
       <c r="J359" s="1"/>
       <c r="K359" s="1"/>
     </row>
-    <row r="360" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="360" spans="1:11" ht="18" customHeight="1">
       <c r="A360" s="1"/>
       <c r="B360" s="2" t="s">
         <v>600</v>
@@ -10746,7 +10760,7 @@
       <c r="J360" s="1"/>
       <c r="K360" s="1"/>
     </row>
-    <row r="361" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="361" spans="1:11" ht="18" customHeight="1">
       <c r="A361" s="1"/>
       <c r="B361" s="2" t="s">
         <v>602</v>
@@ -10765,7 +10779,7 @@
       <c r="J361" s="1"/>
       <c r="K361" s="1"/>
     </row>
-    <row r="362" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="362" spans="1:11" ht="18" customHeight="1">
       <c r="A362" s="6"/>
       <c r="B362" s="2" t="s">
         <v>604</v>
@@ -10786,7 +10800,7 @@
       <c r="J362" s="1"/>
       <c r="K362" s="1"/>
     </row>
-    <row r="363" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="363" spans="1:11" ht="18" customHeight="1">
       <c r="A363" s="6"/>
       <c r="B363" s="2" t="s">
         <v>606</v>
@@ -10805,7 +10819,7 @@
       <c r="J363" s="1"/>
       <c r="K363" s="1"/>
     </row>
-    <row r="364" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="364" spans="1:11" ht="18" customHeight="1">
       <c r="A364" s="6"/>
       <c r="B364" s="2" t="s">
         <v>608</v>
@@ -10824,7 +10838,7 @@
       <c r="J364" s="1"/>
       <c r="K364" s="1"/>
     </row>
-    <row r="365" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="365" spans="1:11" ht="18" customHeight="1">
       <c r="A365" s="6"/>
       <c r="B365" s="2" t="s">
         <v>610</v>
@@ -10843,7 +10857,7 @@
       <c r="J365" s="1"/>
       <c r="K365" s="1"/>
     </row>
-    <row r="366" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="366" spans="1:11" ht="18" customHeight="1">
       <c r="A366" s="6"/>
       <c r="B366" s="2" t="s">
         <v>612</v>
@@ -10862,7 +10876,7 @@
       <c r="J366" s="1"/>
       <c r="K366" s="1"/>
     </row>
-    <row r="367" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="367" spans="1:11" ht="18" customHeight="1">
       <c r="A367" s="6"/>
       <c r="B367" s="2" t="s">
         <v>613</v>
@@ -10881,7 +10895,7 @@
       <c r="J367" s="1"/>
       <c r="K367" s="1"/>
     </row>
-    <row r="368" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="368" spans="1:11" ht="18" customHeight="1">
       <c r="A368" s="6"/>
       <c r="B368" s="2" t="s">
         <v>614</v>
@@ -10900,7 +10914,7 @@
       <c r="J368" s="1"/>
       <c r="K368" s="1"/>
     </row>
-    <row r="369" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="369" spans="1:11" ht="18" customHeight="1">
       <c r="A369" s="6"/>
       <c r="B369" s="2" t="s">
         <v>615</v>
@@ -10919,7 +10933,7 @@
       <c r="J369" s="1"/>
       <c r="K369" s="1"/>
     </row>
-    <row r="370" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="370" spans="1:11" ht="18" customHeight="1">
       <c r="A370" s="1"/>
       <c r="B370" s="2" t="s">
         <v>616</v>
@@ -10938,7 +10952,7 @@
       <c r="J370" s="1"/>
       <c r="K370" s="1"/>
     </row>
-    <row r="371" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="371" spans="1:11" ht="18" customHeight="1">
       <c r="A371" s="6"/>
       <c r="B371" s="2" t="s">
         <v>617</v>
@@ -10957,7 +10971,7 @@
       <c r="J371" s="1"/>
       <c r="K371" s="1"/>
     </row>
-    <row r="372" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="372" spans="1:11" ht="18" customHeight="1">
       <c r="A372" s="1"/>
       <c r="B372" s="2" t="s">
         <v>618</v>
@@ -10976,7 +10990,7 @@
       <c r="J372" s="1"/>
       <c r="K372" s="1"/>
     </row>
-    <row r="373" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="373" spans="1:11" ht="18" customHeight="1">
       <c r="A373" s="6"/>
       <c r="B373" s="2" t="s">
         <v>619</v>
@@ -10995,7 +11009,7 @@
       <c r="J373" s="1"/>
       <c r="K373" s="1"/>
     </row>
-    <row r="374" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="374" spans="1:11" ht="18" customHeight="1">
       <c r="A374" s="6"/>
       <c r="B374" s="2" t="s">
         <v>620</v>
@@ -11014,7 +11028,7 @@
       <c r="J374" s="1"/>
       <c r="K374" s="1"/>
     </row>
-    <row r="375" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="375" spans="1:11" ht="18" customHeight="1">
       <c r="A375" s="6"/>
       <c r="B375" s="2" t="s">
         <v>621</v>
@@ -11033,7 +11047,7 @@
       <c r="J375" s="1"/>
       <c r="K375" s="1"/>
     </row>
-    <row r="376" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="376" spans="1:11" ht="18" customHeight="1">
       <c r="A376" s="6"/>
       <c r="B376" s="2" t="s">
         <v>623</v>
@@ -11052,7 +11066,7 @@
       <c r="J376" s="1"/>
       <c r="K376" s="1"/>
     </row>
-    <row r="377" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="377" spans="1:11" ht="18" customHeight="1">
       <c r="A377" s="1"/>
       <c r="B377" s="2" t="s">
         <v>625</v>
@@ -11073,7 +11087,7 @@
       <c r="J377" s="1"/>
       <c r="K377" s="1"/>
     </row>
-    <row r="378" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="378" spans="1:11" ht="18" customHeight="1">
       <c r="A378" s="6">
         <v>2000</v>
       </c>
@@ -11094,7 +11108,7 @@
       <c r="J378" s="1"/>
       <c r="K378" s="1"/>
     </row>
-    <row r="379" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="379" spans="1:11" ht="18" customHeight="1">
       <c r="A379" s="6">
         <v>200</v>
       </c>
@@ -11115,7 +11129,7 @@
       <c r="J379" s="1"/>
       <c r="K379" s="1"/>
     </row>
-    <row r="380" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="380" spans="1:11" ht="18" customHeight="1">
       <c r="A380" s="6"/>
       <c r="B380" s="2" t="s">
         <v>631</v>
@@ -11134,7 +11148,7 @@
       <c r="J380" s="1"/>
       <c r="K380" s="1"/>
     </row>
-    <row r="381" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="381" spans="1:11" ht="18" customHeight="1">
       <c r="A381" s="6"/>
       <c r="B381" s="2" t="s">
         <v>632</v>
@@ -11155,7 +11169,7 @@
       <c r="J381" s="1"/>
       <c r="K381" s="1"/>
     </row>
-    <row r="382" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="382" spans="1:11" ht="18" customHeight="1">
       <c r="A382" s="1"/>
       <c r="B382" s="2" t="s">
         <v>634</v>
@@ -11174,7 +11188,7 @@
       <c r="J382" s="1"/>
       <c r="K382" s="1"/>
     </row>
-    <row r="383" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="383" spans="1:11" ht="18" customHeight="1">
       <c r="A383" s="1"/>
       <c r="B383" s="2" t="s">
         <v>635</v>
@@ -11193,7 +11207,7 @@
       <c r="J383" s="1"/>
       <c r="K383" s="1"/>
     </row>
-    <row r="384" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="384" spans="1:11" ht="18" customHeight="1">
       <c r="A384" s="1"/>
       <c r="B384" s="2" t="s">
         <v>637</v>
@@ -11214,7 +11228,7 @@
       <c r="J384" s="1"/>
       <c r="K384" s="1"/>
     </row>
-    <row r="385" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="385" spans="1:11" ht="18" customHeight="1">
       <c r="A385" s="6"/>
       <c r="B385" s="2" t="s">
         <v>640</v>
@@ -11233,7 +11247,7 @@
       <c r="J385" s="1"/>
       <c r="K385" s="1"/>
     </row>
-    <row r="386" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="386" spans="1:11" ht="18" customHeight="1">
       <c r="A386" s="1"/>
       <c r="B386" s="2" t="s">
         <v>642</v>
@@ -11252,7 +11266,7 @@
       <c r="J386" s="1"/>
       <c r="K386" s="1"/>
     </row>
-    <row r="387" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="387" spans="1:11" ht="18" customHeight="1">
       <c r="A387" s="1"/>
       <c r="B387" s="2" t="s">
         <v>643</v>
@@ -11271,7 +11285,7 @@
       <c r="J387" s="1"/>
       <c r="K387" s="1"/>
     </row>
-    <row r="388" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="388" spans="1:11" ht="18" customHeight="1">
       <c r="A388" s="6"/>
       <c r="B388" s="2" t="s">
         <v>644</v>
@@ -11290,7 +11304,7 @@
       <c r="J388" s="1"/>
       <c r="K388" s="1"/>
     </row>
-    <row r="389" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="389" spans="1:11" ht="18" customHeight="1">
       <c r="A389" s="6"/>
       <c r="B389" s="2" t="s">
         <v>646</v>
@@ -11309,7 +11323,7 @@
       <c r="J389" s="1"/>
       <c r="K389" s="1"/>
     </row>
-    <row r="390" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="390" spans="1:11" ht="18" customHeight="1">
       <c r="A390" s="6"/>
       <c r="B390" s="2" t="s">
         <v>648</v>
@@ -11328,7 +11342,7 @@
       <c r="J390" s="1"/>
       <c r="K390" s="1"/>
     </row>
-    <row r="391" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="391" spans="1:11" ht="18" customHeight="1">
       <c r="A391" s="6"/>
       <c r="B391" s="2" t="s">
         <v>650</v>
@@ -11347,7 +11361,7 @@
       <c r="J391" s="1"/>
       <c r="K391" s="1"/>
     </row>
-    <row r="392" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="392" spans="1:11" ht="18" customHeight="1">
       <c r="A392" s="6"/>
       <c r="B392" s="2" t="s">
         <v>652</v>
@@ -11366,7 +11380,7 @@
       <c r="J392" s="1"/>
       <c r="K392" s="1"/>
     </row>
-    <row r="393" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="393" spans="1:11" ht="18" customHeight="1">
       <c r="A393" s="6"/>
       <c r="B393" s="2" t="s">
         <v>655</v>
@@ -11537,7 +11551,7 @@
       <c r="J401" s="1"/>
       <c r="K401" s="1"/>
     </row>
-    <row r="402" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="402" spans="1:11" ht="18" customHeight="1">
       <c r="A402" s="6"/>
       <c r="B402" s="2" t="s">
         <v>670</v>
@@ -11556,7 +11570,7 @@
       <c r="J402" s="1"/>
       <c r="K402" s="1"/>
     </row>
-    <row r="403" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="403" spans="1:11" ht="18" customHeight="1">
       <c r="A403" s="6"/>
       <c r="B403" s="2" t="s">
         <v>672</v>
@@ -11575,7 +11589,7 @@
       <c r="J403" s="1"/>
       <c r="K403" s="1"/>
     </row>
-    <row r="404" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="404" spans="1:11" ht="18" customHeight="1">
       <c r="A404" s="6"/>
       <c r="B404" s="2" t="s">
         <v>674</v>
@@ -11594,7 +11608,7 @@
       <c r="J404" s="1"/>
       <c r="K404" s="1"/>
     </row>
-    <row r="405" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="405" spans="1:11" ht="18" customHeight="1">
       <c r="A405" s="6"/>
       <c r="B405" s="2" t="s">
         <v>676</v>
@@ -11615,7 +11629,7 @@
       <c r="J405" s="1"/>
       <c r="K405" s="1"/>
     </row>
-    <row r="406" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="406" spans="1:11" ht="18" customHeight="1">
       <c r="A406" s="1"/>
       <c r="B406" s="2" t="s">
         <v>679</v>
@@ -11634,7 +11648,7 @@
       <c r="J406" s="1"/>
       <c r="K406" s="1"/>
     </row>
-    <row r="407" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="407" spans="1:11" ht="18" customHeight="1">
       <c r="A407" s="1"/>
       <c r="B407" s="2" t="s">
         <v>680</v>
@@ -11653,7 +11667,7 @@
       <c r="J407" s="1"/>
       <c r="K407" s="1"/>
     </row>
-    <row r="408" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="408" spans="1:11" ht="18" customHeight="1">
       <c r="A408" s="6"/>
       <c r="B408" s="2" t="s">
         <v>682</v>
@@ -11672,7 +11686,7 @@
       <c r="J408" s="1"/>
       <c r="K408" s="1"/>
     </row>
-    <row r="409" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="409" spans="1:11" ht="18" customHeight="1">
       <c r="A409" s="6"/>
       <c r="B409" s="2" t="s">
         <v>684</v>
@@ -11691,7 +11705,7 @@
       <c r="J409" s="1"/>
       <c r="K409" s="1"/>
     </row>
-    <row r="410" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="410" spans="1:11" ht="18" customHeight="1">
       <c r="A410" s="1"/>
       <c r="B410" s="2" t="s">
         <v>685</v>
@@ -11710,7 +11724,7 @@
       <c r="J410" s="1"/>
       <c r="K410" s="1"/>
     </row>
-    <row r="411" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="411" spans="1:11" ht="18" customHeight="1">
       <c r="A411" s="6"/>
       <c r="B411" s="2" t="s">
         <v>687</v>
@@ -11729,7 +11743,7 @@
       <c r="J411" s="1"/>
       <c r="K411" s="1"/>
     </row>
-    <row r="412" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="412" spans="1:11" ht="18" customHeight="1">
       <c r="A412" s="1"/>
       <c r="B412" s="2" t="s">
         <v>689</v>
@@ -11748,7 +11762,7 @@
       <c r="J412" s="1"/>
       <c r="K412" s="1"/>
     </row>
-    <row r="413" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="413" spans="1:11" ht="18" customHeight="1">
       <c r="A413" s="6"/>
       <c r="B413" s="2" t="s">
         <v>691</v>
@@ -11769,7 +11783,7 @@
       <c r="J413" s="1"/>
       <c r="K413" s="1"/>
     </row>
-    <row r="414" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="414" spans="1:11" ht="18" customHeight="1">
       <c r="A414" s="6"/>
       <c r="B414" s="2" t="s">
         <v>692</v>
@@ -11788,7 +11802,7 @@
       <c r="J414" s="1"/>
       <c r="K414" s="1"/>
     </row>
-    <row r="415" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="415" spans="1:11" ht="18" customHeight="1">
       <c r="A415" s="6"/>
       <c r="B415" s="2" t="s">
         <v>694</v>
@@ -11807,7 +11821,7 @@
       <c r="J415" s="1"/>
       <c r="K415" s="1"/>
     </row>
-    <row r="416" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="416" spans="1:11" ht="18" customHeight="1">
       <c r="A416" s="6"/>
       <c r="B416" s="2" t="s">
         <v>696</v>
@@ -11828,7 +11842,7 @@
       <c r="J416" s="1"/>
       <c r="K416" s="1"/>
     </row>
-    <row r="417" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="417" spans="1:11" ht="18" customHeight="1">
       <c r="A417" s="6"/>
       <c r="B417" s="2" t="s">
         <v>699</v>
@@ -11847,7 +11861,7 @@
       <c r="J417" s="1"/>
       <c r="K417" s="1"/>
     </row>
-    <row r="418" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="418" spans="1:11" ht="18" customHeight="1">
       <c r="A418" s="1"/>
       <c r="B418" s="2" t="s">
         <v>701</v>
@@ -11866,7 +11880,7 @@
       <c r="J418" s="1"/>
       <c r="K418" s="1"/>
     </row>
-    <row r="419" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="419" spans="1:11" ht="18" customHeight="1">
       <c r="A419" s="6"/>
       <c r="B419" s="2" t="s">
         <v>702</v>
@@ -11885,7 +11899,7 @@
       <c r="J419" s="1"/>
       <c r="K419" s="1"/>
     </row>
-    <row r="420" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="420" spans="1:11" ht="18" customHeight="1">
       <c r="A420" s="1"/>
       <c r="B420" s="2" t="s">
         <v>704</v>
@@ -11904,7 +11918,7 @@
       <c r="J420" s="1"/>
       <c r="K420" s="1"/>
     </row>
-    <row r="421" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="421" spans="1:11" ht="18" customHeight="1">
       <c r="A421" s="1"/>
       <c r="B421" s="2" t="s">
         <v>706</v>
@@ -11923,7 +11937,7 @@
       <c r="J421" s="1"/>
       <c r="K421" s="1"/>
     </row>
-    <row r="422" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="422" spans="1:11" ht="18" customHeight="1">
       <c r="A422" s="1"/>
       <c r="B422" s="2" t="s">
         <v>707</v>
@@ -11942,7 +11956,7 @@
       <c r="J422" s="1"/>
       <c r="K422" s="1"/>
     </row>
-    <row r="423" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="423" spans="1:11" ht="18" customHeight="1">
       <c r="A423" s="1"/>
       <c r="B423" s="2" t="s">
         <v>708</v>
@@ -11961,7 +11975,7 @@
       <c r="J423" s="1"/>
       <c r="K423" s="1"/>
     </row>
-    <row r="424" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="424" spans="1:11" ht="18" customHeight="1">
       <c r="A424" s="6"/>
       <c r="B424" s="2" t="s">
         <v>709</v>
@@ -11980,7 +11994,7 @@
       <c r="J424" s="1"/>
       <c r="K424" s="1"/>
     </row>
-    <row r="425" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="425" spans="1:11" ht="18" customHeight="1">
       <c r="A425" s="6"/>
       <c r="B425" s="2" t="s">
         <v>711</v>
@@ -11999,7 +12013,7 @@
       <c r="J425" s="1"/>
       <c r="K425" s="1"/>
     </row>
-    <row r="426" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="426" spans="1:11" ht="18" customHeight="1">
       <c r="A426" s="6"/>
       <c r="B426" s="2" t="s">
         <v>713</v>
@@ -12018,7 +12032,7 @@
       <c r="J426" s="1"/>
       <c r="K426" s="1"/>
     </row>
-    <row r="427" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="427" spans="1:11" ht="18" customHeight="1">
       <c r="A427" s="1"/>
       <c r="B427" s="2" t="s">
         <v>716</v>
@@ -12037,7 +12051,7 @@
       <c r="J427" s="1"/>
       <c r="K427" s="1"/>
     </row>
-    <row r="428" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="428" spans="1:11" ht="18" customHeight="1">
       <c r="A428" s="6"/>
       <c r="B428" s="2" t="s">
         <v>718</v>
@@ -12056,7 +12070,7 @@
       <c r="J428" s="1"/>
       <c r="K428" s="1"/>
     </row>
-    <row r="429" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="429" spans="1:11" ht="18" customHeight="1">
       <c r="A429" s="6"/>
       <c r="B429" s="2" t="s">
         <v>720</v>
@@ -12075,7 +12089,7 @@
       <c r="J429" s="1"/>
       <c r="K429" s="1"/>
     </row>
-    <row r="430" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="430" spans="1:11" ht="18" customHeight="1">
       <c r="A430" s="6"/>
       <c r="B430" s="2" t="s">
         <v>721</v>
@@ -12094,7 +12108,7 @@
       <c r="J430" s="1"/>
       <c r="K430" s="1"/>
     </row>
-    <row r="431" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="431" spans="1:11" ht="18" customHeight="1">
       <c r="A431" s="6"/>
       <c r="B431" s="2" t="s">
         <v>722</v>
@@ -12113,7 +12127,7 @@
       <c r="J431" s="1"/>
       <c r="K431" s="1"/>
     </row>
-    <row r="432" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="432" spans="1:11" ht="18" customHeight="1">
       <c r="A432" s="6"/>
       <c r="B432" s="2" t="s">
         <v>723</v>
@@ -12132,7 +12146,7 @@
       <c r="J432" s="1"/>
       <c r="K432" s="1"/>
     </row>
-    <row r="433" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="433" spans="1:11" ht="18" customHeight="1">
       <c r="A433" s="6"/>
       <c r="B433" s="2" t="s">
         <v>724</v>
@@ -12151,7 +12165,7 @@
       <c r="J433" s="1"/>
       <c r="K433" s="1"/>
     </row>
-    <row r="434" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="434" spans="1:11" ht="18" customHeight="1">
       <c r="A434" s="6"/>
       <c r="B434" s="2" t="s">
         <v>725</v>
@@ -12170,7 +12184,7 @@
       <c r="J434" s="1"/>
       <c r="K434" s="1"/>
     </row>
-    <row r="435" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="435" spans="1:11" ht="18" customHeight="1">
       <c r="A435" s="6"/>
       <c r="B435" s="2" t="s">
         <v>726</v>
@@ -12189,7 +12203,7 @@
       <c r="J435" s="1"/>
       <c r="K435" s="1"/>
     </row>
-    <row r="436" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="436" spans="1:11" ht="18" customHeight="1">
       <c r="A436" s="6"/>
       <c r="B436" s="2" t="s">
         <v>727</v>
@@ -12208,7 +12222,7 @@
       <c r="J436" s="1"/>
       <c r="K436" s="1"/>
     </row>
-    <row r="437" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="437" spans="1:11" ht="18" customHeight="1">
       <c r="A437" s="6"/>
       <c r="B437" s="2" t="s">
         <v>728</v>
@@ -12227,7 +12241,7 @@
       <c r="J437" s="1"/>
       <c r="K437" s="1"/>
     </row>
-    <row r="438" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="438" spans="1:11" ht="18" customHeight="1">
       <c r="A438" s="1"/>
       <c r="B438" s="2" t="s">
         <v>730</v>
@@ -12246,7 +12260,7 @@
       <c r="J438" s="1"/>
       <c r="K438" s="1"/>
     </row>
-    <row r="439" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="439" spans="1:11" ht="18" customHeight="1">
       <c r="A439" s="1"/>
       <c r="B439" s="2" t="s">
         <v>731</v>
@@ -12265,7 +12279,7 @@
       <c r="J439" s="1"/>
       <c r="K439" s="1"/>
     </row>
-    <row r="440" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="440" spans="1:11" ht="18" customHeight="1">
       <c r="A440" s="6"/>
       <c r="B440" s="2" t="s">
         <v>733</v>
@@ -12284,7 +12298,7 @@
       <c r="J440" s="1"/>
       <c r="K440" s="1"/>
     </row>
-    <row r="441" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="441" spans="1:11" ht="18" customHeight="1">
       <c r="A441" s="1"/>
       <c r="B441" s="2" t="s">
         <v>735</v>
@@ -12305,7 +12319,7 @@
       <c r="J441" s="1"/>
       <c r="K441" s="1"/>
     </row>
-    <row r="442" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="442" spans="1:11" ht="18" customHeight="1">
       <c r="A442" s="6"/>
       <c r="B442" s="2" t="s">
         <v>738</v>
@@ -12326,7 +12340,7 @@
       <c r="J442" s="1"/>
       <c r="K442" s="1"/>
     </row>
-    <row r="443" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="443" spans="1:11" ht="18" customHeight="1">
       <c r="A443" s="6"/>
       <c r="B443" s="2" t="s">
         <v>741</v>
@@ -12345,7 +12359,7 @@
       <c r="J443" s="1"/>
       <c r="K443" s="1"/>
     </row>
-    <row r="444" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="444" spans="1:11" ht="18" customHeight="1">
       <c r="A444" s="6"/>
       <c r="B444" s="2" t="s">
         <v>742</v>
@@ -12364,7 +12378,7 @@
       <c r="J444" s="1"/>
       <c r="K444" s="1"/>
     </row>
-    <row r="445" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="445" spans="1:11" ht="18" customHeight="1">
       <c r="A445" s="6"/>
       <c r="B445" s="2" t="s">
         <v>743</v>
@@ -12383,7 +12397,7 @@
       <c r="J445" s="1"/>
       <c r="K445" s="1"/>
     </row>
-    <row r="446" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="446" spans="1:11" ht="18" customHeight="1">
       <c r="A446" s="6"/>
       <c r="B446" s="2" t="s">
         <v>744</v>
@@ -12402,7 +12416,7 @@
       <c r="J446" s="1"/>
       <c r="K446" s="1"/>
     </row>
-    <row r="447" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="447" spans="1:11" ht="18" customHeight="1">
       <c r="A447" s="6"/>
       <c r="B447" s="2" t="s">
         <v>745</v>
@@ -12421,7 +12435,7 @@
       <c r="J447" s="1"/>
       <c r="K447" s="1"/>
     </row>
-    <row r="448" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="448" spans="1:11" ht="18" customHeight="1">
       <c r="A448" s="6"/>
       <c r="B448" s="2" t="s">
         <v>746</v>
@@ -12440,7 +12454,7 @@
       <c r="J448" s="1"/>
       <c r="K448" s="1"/>
     </row>
-    <row r="449" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="449" spans="1:11" ht="18" customHeight="1">
       <c r="A449" s="6"/>
       <c r="B449" s="2" t="s">
         <v>747</v>
@@ -12459,7 +12473,7 @@
       <c r="J449" s="1"/>
       <c r="K449" s="1"/>
     </row>
-    <row r="450" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="450" spans="1:11" ht="18" customHeight="1">
       <c r="A450" s="6"/>
       <c r="B450" s="18" t="s">
         <v>748</v>
@@ -12478,7 +12492,7 @@
       <c r="J450" s="1"/>
       <c r="K450" s="1"/>
     </row>
-    <row r="451" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="451" spans="1:11" ht="18" customHeight="1">
       <c r="A451" s="6"/>
       <c r="B451" s="2" t="s">
         <v>749</v>
@@ -12497,7 +12511,7 @@
       <c r="J451" s="1"/>
       <c r="K451" s="1"/>
     </row>
-    <row r="452" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="452" spans="1:11" ht="18" customHeight="1">
       <c r="A452" s="6"/>
       <c r="B452" s="2" t="s">
         <v>750</v>
@@ -12516,7 +12530,7 @@
       <c r="J452" s="1"/>
       <c r="K452" s="1"/>
     </row>
-    <row r="453" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="453" spans="1:11" ht="18" customHeight="1">
       <c r="A453" s="6"/>
       <c r="B453" s="2" t="s">
         <v>751</v>
@@ -12535,7 +12549,7 @@
       <c r="J453" s="1"/>
       <c r="K453" s="1"/>
     </row>
-    <row r="454" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="454" spans="1:11" ht="18" customHeight="1">
       <c r="A454" s="6"/>
       <c r="B454" s="2" t="s">
         <v>752</v>
@@ -12554,7 +12568,7 @@
       <c r="J454" s="1"/>
       <c r="K454" s="1"/>
     </row>
-    <row r="455" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="455" spans="1:11" ht="18" customHeight="1">
       <c r="A455" s="6"/>
       <c r="B455" s="2" t="s">
         <v>753</v>
@@ -12573,7 +12587,7 @@
       <c r="J455" s="1"/>
       <c r="K455" s="1"/>
     </row>
-    <row r="456" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="456" spans="1:11" ht="18" customHeight="1">
       <c r="A456" s="6"/>
       <c r="B456" s="2" t="s">
         <v>754</v>
@@ -12592,7 +12606,7 @@
       <c r="J456" s="1"/>
       <c r="K456" s="1"/>
     </row>
-    <row r="457" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="457" spans="1:11" ht="18" customHeight="1">
       <c r="A457" s="6"/>
       <c r="B457" s="2" t="s">
         <v>755</v>
@@ -12611,7 +12625,7 @@
       <c r="J457" s="1"/>
       <c r="K457" s="1"/>
     </row>
-    <row r="458" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="458" spans="1:11" ht="18" customHeight="1">
       <c r="A458" s="6"/>
       <c r="B458" s="2" t="s">
         <v>756</v>
@@ -12630,7 +12644,7 @@
       <c r="J458" s="1"/>
       <c r="K458" s="1"/>
     </row>
-    <row r="459" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="459" spans="1:11" ht="18" customHeight="1">
       <c r="A459" s="6"/>
       <c r="B459" s="2" t="s">
         <v>757</v>
@@ -12649,7 +12663,7 @@
       <c r="J459" s="1"/>
       <c r="K459" s="1"/>
     </row>
-    <row r="460" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="460" spans="1:11" ht="18" customHeight="1">
       <c r="A460" s="6"/>
       <c r="B460" s="2" t="s">
         <v>758</v>
@@ -12668,7 +12682,7 @@
       <c r="J460" s="1"/>
       <c r="K460" s="1"/>
     </row>
-    <row r="461" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="461" spans="1:11" ht="18" customHeight="1">
       <c r="A461" s="1"/>
       <c r="B461" s="2" t="s">
         <v>759</v>
@@ -12687,7 +12701,7 @@
       <c r="J461" s="1"/>
       <c r="K461" s="1"/>
     </row>
-    <row r="462" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="462" spans="1:11" ht="18" customHeight="1">
       <c r="A462" s="6"/>
       <c r="B462" s="2" t="s">
         <v>760</v>
@@ -12706,7 +12720,7 @@
       <c r="J462" s="1"/>
       <c r="K462" s="1"/>
     </row>
-    <row r="463" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="463" spans="1:11" ht="18" customHeight="1">
       <c r="A463" s="6"/>
       <c r="B463" s="2" t="s">
         <v>761</v>
@@ -12725,7 +12739,7 @@
       <c r="J463" s="1"/>
       <c r="K463" s="1"/>
     </row>
-    <row r="464" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="464" spans="1:11" ht="18" customHeight="1">
       <c r="A464" s="6"/>
       <c r="B464" s="2" t="s">
         <v>762</v>
@@ -12744,7 +12758,7 @@
       <c r="J464" s="1"/>
       <c r="K464" s="1"/>
     </row>
-    <row r="465" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="465" spans="1:11" ht="18" customHeight="1">
       <c r="A465" s="6"/>
       <c r="B465" s="2" t="s">
         <v>763</v>
@@ -12782,7 +12796,7 @@
       <c r="J466" s="1"/>
       <c r="K466" s="1"/>
     </row>
-    <row r="467" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="467" spans="1:11" ht="18" customHeight="1">
       <c r="A467" s="1"/>
       <c r="B467" s="2" t="s">
         <v>766</v>
@@ -12803,7 +12817,7 @@
       <c r="J467" s="1"/>
       <c r="K467" s="1"/>
     </row>
-    <row r="468" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="468" spans="1:11" ht="18" customHeight="1">
       <c r="A468" s="1"/>
       <c r="B468" s="2" t="s">
         <v>768</v>
@@ -12822,7 +12836,7 @@
       <c r="J468" s="1"/>
       <c r="K468" s="1"/>
     </row>
-    <row r="469" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="469" spans="1:11" ht="18" customHeight="1">
       <c r="A469" s="6"/>
       <c r="B469" s="2" t="s">
         <v>769</v>
@@ -12843,7 +12857,7 @@
       <c r="J469" s="1"/>
       <c r="K469" s="1"/>
     </row>
-    <row r="470" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="470" spans="1:11" ht="18" customHeight="1">
       <c r="A470" s="1"/>
       <c r="B470" s="2" t="s">
         <v>770</v>
@@ -12862,7 +12876,7 @@
       <c r="J470" s="1"/>
       <c r="K470" s="1"/>
     </row>
-    <row r="471" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="471" spans="1:11" ht="18" customHeight="1">
       <c r="A471" s="1"/>
       <c r="B471" s="2" t="s">
         <v>771</v>
@@ -12881,7 +12895,7 @@
       <c r="J471" s="1"/>
       <c r="K471" s="1"/>
     </row>
-    <row r="472" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="472" spans="1:11" ht="18" customHeight="1">
       <c r="A472" s="1"/>
       <c r="B472" s="2" t="s">
         <v>772</v>
@@ -12900,7 +12914,7 @@
       <c r="J472" s="1"/>
       <c r="K472" s="1"/>
     </row>
-    <row r="473" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="473" spans="1:11" ht="18" customHeight="1">
       <c r="A473" s="1"/>
       <c r="B473" s="2" t="s">
         <v>773</v>
@@ -12919,7 +12933,7 @@
       <c r="J473" s="1"/>
       <c r="K473" s="1"/>
     </row>
-    <row r="474" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="474" spans="1:11" ht="18" customHeight="1">
       <c r="A474" s="6"/>
       <c r="B474" s="2" t="s">
         <v>774</v>
@@ -12938,7 +12952,7 @@
       <c r="J474" s="1"/>
       <c r="K474" s="1"/>
     </row>
-    <row r="475" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="475" spans="1:11" ht="18" customHeight="1">
       <c r="A475" s="6"/>
       <c r="B475" s="2" t="s">
         <v>775</v>
@@ -12957,7 +12971,7 @@
       <c r="J475" s="1"/>
       <c r="K475" s="1"/>
     </row>
-    <row r="476" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="476" spans="1:11" ht="18" customHeight="1">
       <c r="A476" s="6"/>
       <c r="B476" s="2" t="s">
         <v>776</v>
@@ -12976,7 +12990,7 @@
       <c r="J476" s="1"/>
       <c r="K476" s="1"/>
     </row>
-    <row r="477" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="477" spans="1:11" ht="18" customHeight="1">
       <c r="A477" s="6"/>
       <c r="B477" s="2" t="s">
         <v>777</v>
@@ -12995,7 +13009,7 @@
       <c r="J477" s="1"/>
       <c r="K477" s="1"/>
     </row>
-    <row r="478" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="478" spans="1:11" ht="18" customHeight="1">
       <c r="A478" s="1"/>
       <c r="B478" s="2" t="s">
         <v>778</v>
@@ -13014,7 +13028,7 @@
       <c r="J478" s="1"/>
       <c r="K478" s="1"/>
     </row>
-    <row r="479" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="479" spans="1:11" ht="18" customHeight="1">
       <c r="A479" s="1"/>
       <c r="B479" s="2" t="s">
         <v>779</v>
@@ -13033,7 +13047,7 @@
       <c r="J479" s="1"/>
       <c r="K479" s="1"/>
     </row>
-    <row r="480" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="480" spans="1:11" ht="18" customHeight="1">
       <c r="A480" s="1"/>
       <c r="B480" s="2" t="s">
         <v>780</v>
@@ -13052,7 +13066,7 @@
       <c r="J480" s="1"/>
       <c r="K480" s="1"/>
     </row>
-    <row r="481" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="481" spans="1:11" ht="18" customHeight="1">
       <c r="A481" s="1"/>
       <c r="B481" s="2" t="s">
         <v>781</v>
@@ -13071,7 +13085,7 @@
       <c r="J481" s="1"/>
       <c r="K481" s="1"/>
     </row>
-    <row r="482" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="482" spans="1:11" ht="18" customHeight="1">
       <c r="A482" s="6"/>
       <c r="B482" s="2" t="s">
         <v>782</v>
@@ -13090,7 +13104,7 @@
       <c r="J482" s="1"/>
       <c r="K482" s="1"/>
     </row>
-    <row r="483" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="483" spans="1:11" ht="18" customHeight="1">
       <c r="A483" s="1"/>
       <c r="B483" s="2" t="s">
         <v>783</v>
@@ -13109,7 +13123,7 @@
       <c r="J483" s="1"/>
       <c r="K483" s="1"/>
     </row>
-    <row r="484" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="484" spans="1:11" ht="18" customHeight="1">
       <c r="A484" s="6"/>
       <c r="B484" s="2" t="s">
         <v>784</v>
@@ -13128,7 +13142,7 @@
       <c r="J484" s="1"/>
       <c r="K484" s="1"/>
     </row>
-    <row r="485" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="485" spans="1:11" ht="18" customHeight="1">
       <c r="A485" s="6"/>
       <c r="B485" s="2" t="s">
         <v>786</v>
@@ -13149,7 +13163,7 @@
       <c r="J485" s="1"/>
       <c r="K485" s="1"/>
     </row>
-    <row r="486" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="486" spans="1:11" ht="18" customHeight="1">
       <c r="A486" s="6"/>
       <c r="B486" s="2" t="s">
         <v>788</v>
@@ -13168,7 +13182,7 @@
       <c r="J486" s="1"/>
       <c r="K486" s="1"/>
     </row>
-    <row r="487" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="487" spans="1:11" ht="18" customHeight="1">
       <c r="A487" s="6"/>
       <c r="B487" s="2" t="s">
         <v>790</v>
@@ -13187,7 +13201,7 @@
       <c r="J487" s="1"/>
       <c r="K487" s="1"/>
     </row>
-    <row r="488" spans="1:11" ht="18" hidden="1" customHeight="1">
+    <row r="488" spans="1:11" ht="18" customHeight="1">
       <c r="A488" s="1"/>
       <c r="B488" s="2" t="s">
         <v>792</v>
@@ -13208,10 +13222,16 @@
     </row>
     <row r="489" spans="1:11" ht="15.5">
       <c r="A489" s="1"/>
-      <c r="B489" s="2"/>
-      <c r="C489" s="3"/>
+      <c r="B489" s="2" t="s">
+        <v>854</v>
+      </c>
+      <c r="C489" s="3" t="s">
+        <v>855</v>
+      </c>
       <c r="D489" s="4"/>
-      <c r="E489" s="5"/>
+      <c r="E489" s="5" t="s">
+        <v>856</v>
+      </c>
       <c r="F489" s="1"/>
       <c r="G489" s="1"/>
       <c r="H489" s="1"/>
@@ -13234,17 +13254,6 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:F488" xr:uid="{00000000-0009-0000-0000-000000000000}">
-    <filterColumn colId="2">
-      <filters>
-        <filter val="胡杨林"/>
-        <filter val="杨丞琳"/>
-        <filter val="杨幂"/>
-        <filter val="杨培安"/>
-        <filter val="杨沛宜"/>
-        <filter val="杨千嬅"/>
-        <filter val="周杰伦,杨瑞代"/>
-      </filters>
-    </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F488">
       <sortCondition ref="C1:C488"/>
     </sortState>

--- a/幽灵歌单整理.xlsx
+++ b/幽灵歌单整理.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Ksoftware\v-song-list-main\v-song-list9\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Ksoftware\v-song-list-main\v-song-list9\v-song-list9\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07D8E30C-CCA6-42DF-91B1-70996DA76930}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F2F795A-5307-4215-AE6B-EF918BC136E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3179,7 +3179,7 @@
     <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
-    <t>国语</t>
+    <t>国语，流行</t>
     <phoneticPr fontId="17" type="noConversion"/>
   </si>
 </sst>
